--- a/public/BD_Tracker_Live Document.xlsx
+++ b/public/BD_Tracker_Live Document.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eedadvisory-my.sharepoint.com/personal/mkisaka_eedadvisory_com/Documents/EED/BD/Tracker/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="245" documentId="13_ncr:1_{CBF42D84-10F5-4E73-A6DC-76A9CE071D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{237903C0-A251-411C-9E2C-201FD0804A34}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F31D57-4241-4BCA-8C8A-BE05BE5F5770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{1556F1C6-BB24-42EB-9F2A-F607E6E74C17}"/>
   </bookViews>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Teams!$A$1:$E$9</definedName>
     <definedName name="Status">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3880" uniqueCount="990">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3982" uniqueCount="1002">
   <si>
     <t>Serial Number</t>
   </si>
@@ -3325,6 +3325,42 @@
   </si>
   <si>
     <t>Dr. Catherine Majale</t>
+  </si>
+  <si>
+    <t>Impact Hub</t>
+  </si>
+  <si>
+    <t>Landscape Research and Analysis for the Advancing Agricultural Circularity Programme in Kenya</t>
+  </si>
+  <si>
+    <t>Outcomes-Based Approach to Mobilize Clean Cooking Investments</t>
+  </si>
+  <si>
+    <t>Adrian Ghilardi, Marc Jeuland</t>
+  </si>
+  <si>
+    <t>The Millennium Water Alliance (MWA)</t>
+  </si>
+  <si>
+    <t>Evaluation of the DRIP FUNDI Program</t>
+  </si>
+  <si>
+    <t>Ministry of Energy</t>
+  </si>
+  <si>
+    <t>Appui à la mise en oeuvre de la Stratégie nationale de Transition énergétique juste (JET) et de la Stratégie nationale d'achèvement de l'accès universel à l'électricité à l'horizon 2029</t>
+  </si>
+  <si>
+    <t>RECRUITMENT OF A CONSULTANT (FIRM) FOR A STUDY ON THE COMPARISON AND HARMONISATION OF NATIONAL ELECTRICITY TARIFFS AND TARIFF PRINCIPLES AND THE DEVELOPMENT OF A FRAMEWORK AND TOOL FOR ASSESSING COST REFLECTIVITY.</t>
+  </si>
+  <si>
+    <t>Central Africa Member States</t>
+  </si>
+  <si>
+    <t>Preparation of Climate-Resilient and Energy-Efficient Cooling Investments in Malawi</t>
+  </si>
+  <si>
+    <t>CEM</t>
   </si>
 </sst>
 </file>
@@ -4329,7 +4365,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="142">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4738,9 +4774,6 @@
     <xf numFmtId="14" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4748,6 +4781,24 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="44">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -5697,7 +5748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D008F4A-4F7B-4D00-B2B1-5D1E4C2AF094}">
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr defaultColWidth="47.54296875" defaultRowHeight="13" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.36328125" style="53" customWidth="1"/>
@@ -9155,60 +9206,286 @@
       <c r="C61" s="128" t="s">
         <v>87</v>
       </c>
-      <c r="D61" s="135" t="s">
+      <c r="D61" s="143" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="135" t="s">
+      <c r="E61" s="143" t="s">
         <v>562</v>
       </c>
-      <c r="F61" s="136" t="s">
+      <c r="F61" s="144" t="s">
         <v>940</v>
       </c>
-      <c r="G61" s="135" t="s">
+      <c r="G61" s="143" t="s">
         <v>79</v>
       </c>
-      <c r="H61" s="135" t="s">
+      <c r="H61" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="I61" s="135" t="s">
+      <c r="I61" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="J61" s="135" t="s">
+      <c r="J61" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="K61" s="135" t="s">
+      <c r="K61" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="L61" s="135"/>
-      <c r="M61" s="137">
+      <c r="L61" s="143"/>
+      <c r="M61" s="145">
         <v>46182</v>
       </c>
-      <c r="N61" s="135" t="s">
+      <c r="N61" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="O61" s="135"/>
-      <c r="P61" s="135"/>
-      <c r="Q61" s="135" t="s">
+      <c r="O61" s="143"/>
+      <c r="P61" s="143"/>
+      <c r="Q61" s="143" t="s">
         <v>568</v>
       </c>
-      <c r="R61" s="135" t="s">
+      <c r="R61" s="143" t="s">
         <v>53</v>
       </c>
-      <c r="S61" s="135" t="s">
+      <c r="S61" s="143" t="s">
         <v>41</v>
       </c>
-      <c r="T61" s="135"/>
-      <c r="U61" s="135"/>
+      <c r="T61" s="143"/>
+      <c r="U61" s="143"/>
+    </row>
+    <row r="62" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="121">
+        <v>61</v>
+      </c>
+      <c r="B62" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C62" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D62" s="135" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" s="135" t="s">
+        <v>996</v>
+      </c>
+      <c r="F62" s="136" t="s">
+        <v>997</v>
+      </c>
+      <c r="G62" s="135" t="s">
+        <v>34</v>
+      </c>
+      <c r="H62" s="135" t="s">
+        <v>80</v>
+      </c>
+      <c r="I62" s="135" t="s">
+        <v>23</v>
+      </c>
+      <c r="J62" s="135" t="s">
+        <v>106</v>
+      </c>
+      <c r="K62" s="135" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" s="135"/>
+      <c r="M62" s="146"/>
+      <c r="N62" s="135" t="s">
+        <v>962</v>
+      </c>
+      <c r="O62" s="135"/>
+      <c r="P62" s="135" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q62" s="135" t="s">
+        <v>899</v>
+      </c>
+      <c r="R62" s="135" t="s">
+        <v>523</v>
+      </c>
+      <c r="S62" s="135" t="s">
+        <v>78</v>
+      </c>
+      <c r="T62" s="135" t="s">
+        <v>49</v>
+      </c>
+      <c r="U62" s="135">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="121">
+        <v>62</v>
+      </c>
+      <c r="B63" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C63" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D63" s="135" t="s">
+        <v>959</v>
+      </c>
+      <c r="E63" s="135" t="s">
+        <v>960</v>
+      </c>
+      <c r="F63" s="136" t="s">
+        <v>961</v>
+      </c>
+      <c r="G63" s="135" t="s">
+        <v>34</v>
+      </c>
+      <c r="H63" s="135" t="s">
+        <v>80</v>
+      </c>
+      <c r="I63" s="135" t="s">
+        <v>23</v>
+      </c>
+      <c r="J63" s="135" t="s">
+        <v>106</v>
+      </c>
+      <c r="K63" s="135" t="s">
+        <v>85</v>
+      </c>
+      <c r="L63" s="135"/>
+      <c r="M63" s="146"/>
+      <c r="N63" s="135" t="s">
+        <v>962</v>
+      </c>
+      <c r="O63" s="135"/>
+      <c r="P63" s="135"/>
+      <c r="Q63" s="135"/>
+      <c r="R63" s="135" t="s">
+        <v>523</v>
+      </c>
+      <c r="S63" s="135" t="s">
+        <v>78</v>
+      </c>
+      <c r="T63" s="135" t="s">
+        <v>49</v>
+      </c>
+      <c r="U63" s="135"/>
+    </row>
+    <row r="64" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="121">
+        <v>63</v>
+      </c>
+      <c r="B64" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C64" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D64" s="135" t="s">
+        <v>19</v>
+      </c>
+      <c r="E64" s="135" t="s">
+        <v>42</v>
+      </c>
+      <c r="F64" s="136" t="s">
+        <v>998</v>
+      </c>
+      <c r="G64" s="135" t="s">
+        <v>590</v>
+      </c>
+      <c r="H64" s="135" t="s">
+        <v>40</v>
+      </c>
+      <c r="I64" s="135" t="s">
+        <v>23</v>
+      </c>
+      <c r="J64" s="135" t="s">
+        <v>999</v>
+      </c>
+      <c r="K64" s="135" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" s="135"/>
+      <c r="M64" s="146"/>
+      <c r="N64" s="135" t="s">
+        <v>47</v>
+      </c>
+      <c r="O64" s="135"/>
+      <c r="P64" s="135"/>
+      <c r="Q64" s="135"/>
+      <c r="R64" s="135" t="s">
+        <v>962</v>
+      </c>
+      <c r="S64" s="135" t="s">
+        <v>523</v>
+      </c>
+      <c r="T64" s="135"/>
+      <c r="U64" s="135">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="121">
+        <v>64</v>
+      </c>
+      <c r="B65" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C65" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D65" s="135" t="s">
+        <v>55</v>
+      </c>
+      <c r="E65" s="135" t="s">
+        <v>20</v>
+      </c>
+      <c r="F65" s="136" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G65" s="135" t="s">
+        <v>34</v>
+      </c>
+      <c r="H65" s="135" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" s="135" t="s">
+        <v>23</v>
+      </c>
+      <c r="J65" s="135" t="s">
+        <v>97</v>
+      </c>
+      <c r="K65" s="135" t="s">
+        <v>58</v>
+      </c>
+      <c r="L65" s="135"/>
+      <c r="M65" s="146">
+        <v>46198</v>
+      </c>
+      <c r="N65" s="135" t="s">
+        <v>36</v>
+      </c>
+      <c r="O65" s="135" t="s">
+        <v>36</v>
+      </c>
+      <c r="P65" s="135" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q65" s="135" t="s">
+        <v>1001</v>
+      </c>
+      <c r="R65" s="135" t="s">
+        <v>36</v>
+      </c>
+      <c r="S65" s="135" t="s">
+        <v>37</v>
+      </c>
+      <c r="T65" s="135" t="s">
+        <v>95</v>
+      </c>
+      <c r="U65" s="135"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:V57" xr:uid="{0D008F4A-4F7B-4D00-B2B1-5D1E4C2AF094}"/>
   <phoneticPr fontId="42" type="noConversion"/>
   <dataValidations count="7">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M49:M1048576 U49:U1048576 U1" xr:uid="{53C03EB9-171C-49BE-A2B1-76486CCC2F4C}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1 U49:U61 U66:U1048576 M49:M61 M66:M1048576" xr:uid="{53C03EB9-171C-49BE-A2B1-76486CCC2F4C}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="It should be in months" sqref="U2:U26 V1 U28:U56 U58:U61 V62:V1048576" xr:uid="{AC6A3088-3943-48BB-8581-3772A4F7A436}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="It should be in months" sqref="U2:U26 V1 U28:U56 U58:U61 V66:V1048576" xr:uid="{AC6A3088-3943-48BB-8581-3772A4F7A436}">
       <formula1>1</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -9240,7 +9517,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7F4377-AB0D-4AD1-9A42-D0995505B602}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W222"/>
+  <dimension ref="A1:W217"/>
   <sheetFormatPr defaultRowHeight="10" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.81640625" style="53" bestFit="1" customWidth="1"/>
@@ -17310,7 +17587,7 @@
       <c r="W128" s="36"/>
     </row>
     <row r="129" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="140">
+      <c r="A129" s="139">
         <v>33</v>
       </c>
       <c r="B129" s="51">
@@ -17369,7 +17646,7 @@
       </c>
     </row>
     <row r="130" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="139">
+      <c r="A130" s="138">
         <v>34</v>
       </c>
       <c r="B130" s="51">
@@ -17430,7 +17707,7 @@
       </c>
     </row>
     <row r="131" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="139">
+      <c r="A131" s="138">
         <v>35</v>
       </c>
       <c r="B131" s="51">
@@ -17499,7 +17776,7 @@
       </c>
     </row>
     <row r="132" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="139">
+      <c r="A132" s="138">
         <v>36</v>
       </c>
       <c r="B132" s="51">
@@ -17564,7 +17841,7 @@
       </c>
     </row>
     <row r="133" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="139">
+      <c r="A133" s="138">
         <v>37</v>
       </c>
       <c r="B133" s="51">
@@ -17631,7 +17908,7 @@
       </c>
     </row>
     <row r="134" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="139">
+      <c r="A134" s="138">
         <v>38</v>
       </c>
       <c r="B134" s="51">
@@ -17702,7 +17979,7 @@
       </c>
     </row>
     <row r="135" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="139">
+      <c r="A135" s="138">
         <v>38</v>
       </c>
       <c r="B135" s="51">
@@ -17769,7 +18046,7 @@
       </c>
     </row>
     <row r="136" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="139">
+      <c r="A136" s="138">
         <v>39</v>
       </c>
       <c r="B136" s="51">
@@ -17834,7 +18111,7 @@
       </c>
     </row>
     <row r="137" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="139">
+      <c r="A137" s="138">
         <v>40</v>
       </c>
       <c r="B137" s="51">
@@ -17895,7 +18172,7 @@
       <c r="W137" s="36"/>
     </row>
     <row r="138" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="139">
+      <c r="A138" s="138">
         <v>41</v>
       </c>
       <c r="B138" s="51">
@@ -17960,7 +18237,7 @@
       <c r="W138" s="36"/>
     </row>
     <row r="139" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="139">
+      <c r="A139" s="138">
         <v>42</v>
       </c>
       <c r="B139" s="51">
@@ -18025,7 +18302,7 @@
       </c>
     </row>
     <row r="140" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="139">
+      <c r="A140" s="138">
         <v>43</v>
       </c>
       <c r="B140" s="51">
@@ -18084,7 +18361,7 @@
       </c>
     </row>
     <row r="141" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="139">
+      <c r="A141" s="138">
         <v>44</v>
       </c>
       <c r="B141" s="51">
@@ -18149,7 +18426,7 @@
       </c>
     </row>
     <row r="142" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="139">
+      <c r="A142" s="138">
         <v>45</v>
       </c>
       <c r="B142" s="51">
@@ -18211,7 +18488,7 @@
       </c>
     </row>
     <row r="143" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="139">
+      <c r="A143" s="138">
         <v>46</v>
       </c>
       <c r="B143" s="51">
@@ -18279,7 +18556,7 @@
       </c>
     </row>
     <row r="144" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="139">
+      <c r="A144" s="138">
         <v>47</v>
       </c>
       <c r="B144" s="51">
@@ -18344,7 +18621,7 @@
       </c>
     </row>
     <row r="145" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="139">
+      <c r="A145" s="138">
         <v>48</v>
       </c>
       <c r="B145" s="51">
@@ -18394,7 +18671,7 @@
       </c>
     </row>
     <row r="146" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="139">
+      <c r="A146" s="138">
         <v>49</v>
       </c>
       <c r="B146" s="51">
@@ -18444,7 +18721,7 @@
       </c>
     </row>
     <row r="147" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="139">
+      <c r="A147" s="138">
         <v>50</v>
       </c>
       <c r="B147" s="51">
@@ -18506,7 +18783,7 @@
       </c>
     </row>
     <row r="148" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="139">
+      <c r="A148" s="138">
         <v>51</v>
       </c>
       <c r="B148" s="51">
@@ -18574,7 +18851,7 @@
       </c>
     </row>
     <row r="149" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="139">
+      <c r="A149" s="138">
         <v>52</v>
       </c>
       <c r="B149" s="51">
@@ -18639,7 +18916,7 @@
       </c>
     </row>
     <row r="150" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="139">
+      <c r="A150" s="138">
         <v>53</v>
       </c>
       <c r="B150" s="51">
@@ -18701,7 +18978,7 @@
       </c>
     </row>
     <row r="151" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="139">
+      <c r="A151" s="138">
         <v>54</v>
       </c>
       <c r="B151" s="51">
@@ -18766,7 +19043,7 @@
       </c>
     </row>
     <row r="152" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="139">
+      <c r="A152" s="138">
         <v>55</v>
       </c>
       <c r="B152" s="51">
@@ -18831,7 +19108,7 @@
       </c>
     </row>
     <row r="153" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="139">
+      <c r="A153" s="138">
         <v>56</v>
       </c>
       <c r="B153" s="51">
@@ -18899,7 +19176,7 @@
       </c>
     </row>
     <row r="154" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="139">
+      <c r="A154" s="138">
         <v>54</v>
       </c>
       <c r="B154" s="51">
@@ -18958,7 +19235,7 @@
       </c>
     </row>
     <row r="155" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="139">
+      <c r="A155" s="138">
         <v>55</v>
       </c>
       <c r="B155" s="51">
@@ -19020,7 +19297,7 @@
       </c>
     </row>
     <row r="156" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="139">
+      <c r="A156" s="138">
         <v>56</v>
       </c>
       <c r="B156" s="51">
@@ -19070,7 +19347,7 @@
       </c>
     </row>
     <row r="157" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="139">
+      <c r="A157" s="138">
         <v>57</v>
       </c>
       <c r="B157" s="51">
@@ -19120,7 +19397,7 @@
       </c>
     </row>
     <row r="158" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="53">
+      <c r="A158" s="138">
         <v>58</v>
       </c>
       <c r="B158" s="51">
@@ -19185,57 +19462,234 @@
       </c>
     </row>
     <row r="159" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="138"/>
+      <c r="A159" s="138">
+        <v>59</v>
+      </c>
+      <c r="B159" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C159" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D159" s="53" t="s">
+        <v>30</v>
+      </c>
+      <c r="E159" s="53" t="s">
+        <v>990</v>
+      </c>
+      <c r="F159" s="57" t="s">
+        <v>991</v>
+      </c>
+      <c r="G159" s="53" t="s">
+        <v>74</v>
+      </c>
+      <c r="H159" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="I159" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="J159" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="K159" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="L159" s="141">
+        <v>46195</v>
+      </c>
+      <c r="M159" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="N159" s="53" t="s">
+        <v>32</v>
+      </c>
+      <c r="O159" s="53" t="s">
+        <v>89</v>
+      </c>
+      <c r="R159" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="S159" s="53" t="s">
+        <v>28</v>
+      </c>
+      <c r="U159" s="53" t="s">
+        <v>95</v>
+      </c>
+      <c r="W159" s="53">
+        <v>1</v>
+      </c>
     </row>
     <row r="160" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="5"/>
-    </row>
-    <row r="161" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="5"/>
-    </row>
-    <row r="162" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="138">
+        <v>60</v>
+      </c>
+      <c r="B160" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C160" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D160" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="E160" s="53" t="s">
+        <v>20</v>
+      </c>
+      <c r="F160" s="57" t="s">
+        <v>992</v>
+      </c>
+      <c r="G160" s="53" t="s">
+        <v>56</v>
+      </c>
+      <c r="H160" s="53" t="s">
+        <v>22</v>
+      </c>
+      <c r="I160" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="J160" s="53" t="s">
+        <v>978</v>
+      </c>
+      <c r="K160" s="53" t="s">
+        <v>25</v>
+      </c>
+      <c r="L160" s="141">
+        <v>46150</v>
+      </c>
+      <c r="M160" s="67" t="s">
+        <v>506</v>
+      </c>
+      <c r="N160" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="O160" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q160" s="53" t="s">
+        <v>993</v>
+      </c>
+      <c r="R160" s="53" t="s">
+        <v>47</v>
+      </c>
+      <c r="S160" s="53" t="s">
+        <v>90</v>
+      </c>
+      <c r="T160" s="142">
+        <v>300474.76</v>
+      </c>
+      <c r="U160" s="53" t="s">
+        <v>70</v>
+      </c>
+      <c r="W160" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A161" s="138">
+        <v>61</v>
+      </c>
+      <c r="B161" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C161" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D161" s="53" t="s">
+        <v>83</v>
+      </c>
+      <c r="E161" s="53" t="s">
+        <v>994</v>
+      </c>
+      <c r="F161" s="57" t="s">
+        <v>995</v>
+      </c>
+      <c r="G161" s="53" t="s">
+        <v>39</v>
+      </c>
+      <c r="H161" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="I161" s="53" t="s">
+        <v>23</v>
+      </c>
+      <c r="J161" s="53" t="s">
+        <v>24</v>
+      </c>
+      <c r="K161" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="L161" s="141">
+        <v>46181</v>
+      </c>
+      <c r="M161" s="67" t="s">
+        <v>46</v>
+      </c>
+      <c r="N161" s="53" t="s">
+        <v>48</v>
+      </c>
+      <c r="O161" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="R161" s="53" t="s">
+        <v>59</v>
+      </c>
+      <c r="S161" s="53" t="s">
+        <v>54</v>
+      </c>
+      <c r="T161" s="142">
+        <v>80568.2</v>
+      </c>
+      <c r="U161" s="53" t="s">
+        <v>946</v>
+      </c>
+      <c r="W161" s="53">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
     <row r="177" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
@@ -19360,21 +19814,6 @@
     </row>
     <row r="217" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="5"/>
-    </row>
-    <row r="218" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="5"/>
-    </row>
-    <row r="219" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="5"/>
-    </row>
-    <row r="220" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="5"/>
-    </row>
-    <row r="221" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="5"/>
-    </row>
-    <row r="222" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="5"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W139" xr:uid="{7F7F4377-AB0D-4AD1-9A42-D0995505B602}">
@@ -19386,7 +19825,7 @@
   </autoFilter>
   <phoneticPr fontId="42" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V97:V139 L97:L1048576" xr:uid="{7C384ADE-763A-4BD1-83BF-4E824E178031}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V97:V139 L97:L158 L162:L1048576 U159:U161 M159:M161" xr:uid="{7C384ADE-763A-4BD1-83BF-4E824E178031}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
@@ -19398,7 +19837,7 @@
       <formula1>46023</formula1>
       <formula2>46034</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="It should be in months" sqref="W97:W139 V2:V42 V47:V49" xr:uid="{15211EFD-2049-40DA-B54C-BAC6674745A7}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="It should be in months" sqref="W97:W139 V2:V42 V47:V49 V159:V161" xr:uid="{15211EFD-2049-40DA-B54C-BAC6674745A7}">
       <formula1>1</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -24270,7 +24709,7 @@
       <c r="A5" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="141" t="s">
+      <c r="B5" s="140" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="26" t="s">
@@ -24334,7 +24773,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="141"/>
+      <c r="A10" s="140"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E9" xr:uid="{B83AD578-DA28-4F78-8FD4-6B585E562D50}"/>
@@ -24344,8 +24783,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002408E3D2F54C53489D9AB6139CAEF0B9" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5b53137c13edb3a93c807c37fc810ee8">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d24e2f5-a44a-4509-8e3a-4f36d63f9f8f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4989bacb2ae110786df28b14aa57fc34" ns2:_="">
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002408E3D2F54C53489D9AB6139CAEF0B9" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="492e2bda549b44b2f704032f7767c399">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d24e2f5-a44a-4509-8e3a-4f36d63f9f8f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="240da83a898570f75363da29bdb62103" ns2:_="">
     <xsd:import namespace="9d24e2f5-a44a-4509-8e3a-4f36d63f9f8f"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -24481,15 +24929,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -24497,7 +24936,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{501692EB-DD9D-45CE-A8FF-2AFFA191EB74}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83EAEF3C-2011-4D39-879E-EC8263732E2D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F46D618-D708-4DF1-99B7-BBB132EA2863}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -24514,14 +24961,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83EAEF3C-2011-4D39-879E-EC8263732E2D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D7E94F3-90D7-4B0A-A68A-E7EE44295A2C}">
   <ds:schemaRefs>

--- a/public/BD_Tracker_Live Document.xlsx
+++ b/public/BD_Tracker_Live Document.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eedadvisory-my.sharepoint.com/personal/mkisaka_eedadvisory_com/Documents/EED/BD/Tracker/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18F31D57-4241-4BCA-8C8A-BE05BE5F5770}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="293" documentId="13_ncr:1_{CBF42D84-10F5-4E73-A6DC-76A9CE071D54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB16804C-BEB5-4D20-809B-6965278064B9}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" xr2:uid="{1556F1C6-BB24-42EB-9F2A-F607E6E74C17}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="12220" activeTab="1" xr2:uid="{1556F1C6-BB24-42EB-9F2A-F607E6E74C17}"/>
   </bookViews>
   <sheets>
     <sheet name="EOIs Tracker 2025" sheetId="5" r:id="rId1"/>
@@ -27,7 +27,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Teams!$A$1:$E$9</definedName>
     <definedName name="Status">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -346,7 +346,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3982" uniqueCount="1002">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4243" uniqueCount="1048">
   <si>
     <t>Serial Number</t>
   </si>
@@ -3327,6 +3327,78 @@
     <t>Dr. Catherine Majale</t>
   </si>
   <si>
+    <t>Ministry of Energy</t>
+  </si>
+  <si>
+    <t>Appui à la mise en oeuvre de la Stratégie nationale de Transition énergétique juste (JET) et de la Stratégie nationale d'achèvement de l'accès universel à l'électricité à l'horizon 2029</t>
+  </si>
+  <si>
+    <t>RECRUITMENT OF A CONSULTANT (FIRM) FOR A STUDY ON THE COMPARISON AND HARMONISATION OF NATIONAL ELECTRICITY TARIFFS AND TARIFF PRINCIPLES AND THE DEVELOPMENT OF A FRAMEWORK AND TOOL FOR ASSESSING COST REFLECTIVITY.</t>
+  </si>
+  <si>
+    <t>Central Africa Member States</t>
+  </si>
+  <si>
+    <t>Preparation of Climate-Resilient and Energy-Efficient Cooling Investments in Malawi</t>
+  </si>
+  <si>
+    <t>CEM</t>
+  </si>
+  <si>
+    <t>Évaluation d'impacts des projets ORIO et dessalement de l'eau saumâtre de Gandiaye</t>
+  </si>
+  <si>
+    <t>Federal Government of Somalia</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Design of a Results-Based Financing (RBF) Framework under the HARECT Project</t>
+  </si>
+  <si>
+    <t>Cygnum Capital</t>
+  </si>
+  <si>
+    <t>Ascent Project Preparation Facility</t>
+  </si>
+  <si>
+    <t>Multi-lateral Development Bank / Private Sector</t>
+  </si>
+  <si>
+    <t>World Bank Group / IFC and GCB Cocoa</t>
+  </si>
+  <si>
+    <t>Consultancy Services for a Biochar Feasibility Assessment</t>
+  </si>
+  <si>
+    <t>Feasibility Study</t>
+  </si>
+  <si>
+    <t>Core(New)</t>
+  </si>
+  <si>
+    <t>Côte d’Ivoire</t>
+  </si>
+  <si>
+    <t>Senam / WBGeProcure RFx Now</t>
+  </si>
+  <si>
+    <t>TBD</t>
+  </si>
+  <si>
+    <t>JW</t>
+  </si>
+  <si>
+    <t>Go / In preparation</t>
+  </si>
+  <si>
+    <t>Hivos / EU SWITCH Kenya Green Tujenge Pamoja</t>
+  </si>
+  <si>
+    <t>Baseline Study of Circular Economy Adoption, Enablers, and Risks in MSMEs across Plastic, Textile, and Organic Waste Value Chains</t>
+  </si>
+  <si>
+    <t>Christine Lucy Majale</t>
+  </si>
+  <si>
     <t>Impact Hub</t>
   </si>
   <si>
@@ -3345,22 +3417,90 @@
     <t>Evaluation of the DRIP FUNDI Program</t>
   </si>
   <si>
-    <t>Ministry of Energy</t>
-  </si>
-  <si>
-    <t>Appui à la mise en oeuvre de la Stratégie nationale de Transition énergétique juste (JET) et de la Stratégie nationale d'achèvement de l'accès universel à l'électricité à l'horizon 2029</t>
-  </si>
-  <si>
-    <t>RECRUITMENT OF A CONSULTANT (FIRM) FOR A STUDY ON THE COMPARISON AND HARMONISATION OF NATIONAL ELECTRICITY TARIFFS AND TARIFF PRINCIPLES AND THE DEVELOPMENT OF A FRAMEWORK AND TOOL FOR ASSESSING COST REFLECTIVITY.</t>
-  </si>
-  <si>
-    <t>Central Africa Member States</t>
-  </si>
-  <si>
-    <t>Preparation of Climate-Resilient and Energy-Efficient Cooling Investments in Malawi</t>
-  </si>
-  <si>
-    <t>CEM</t>
+    <t>Ashden</t>
+  </si>
+  <si>
+    <t>Develop a toolkit for funders and practitioners on inclusive financing and delivery models for energy access in displacement settings. </t>
+  </si>
+  <si>
+    <t>Kenya, Ethiopia, Uganda</t>
+  </si>
+  <si>
+    <t>Appui à la finalisation et à l’opérationnalisation de la Stratégie Nationale de Cuisson Propre (2025–2035)</t>
+  </si>
+  <si>
+    <t>World Bank Portal</t>
+  </si>
+  <si>
+    <t>WWF-Kenya</t>
+  </si>
+  <si>
+    <t>Joint Consultancy to Define the Architecture, Governance, and Capitalization of the Africa Water Resilience Fund (AWRF)</t>
+  </si>
+  <si>
+    <t>Terassos</t>
+  </si>
+  <si>
+    <t>Stichting Clean Energy and Energy Inclusion for Africa</t>
+  </si>
+  <si>
+    <t>Regulatory Mapping Phase II</t>
+  </si>
+  <si>
+    <t>Development of The Gambia's National Clean Cooking Strategy</t>
+  </si>
+  <si>
+    <t>The Gambia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Carbon Market Awarness for SMEs in Uganda </t>
+  </si>
+  <si>
+    <t>Carbon Markets</t>
+  </si>
+  <si>
+    <t>Innovation Village Hub</t>
+  </si>
+  <si>
+    <t>Diocese of Lodwar</t>
+  </si>
+  <si>
+    <t>Strategic and Business Plan for TURWASCO</t>
+  </si>
+  <si>
+    <t>Hivos</t>
+  </si>
+  <si>
+    <t>A Baseline study of circular economy adoption</t>
+  </si>
+  <si>
+    <t>Aruwa Capital</t>
+  </si>
+  <si>
+    <t>Commercial Due Diligence on Project Pine</t>
+  </si>
+  <si>
+    <t>EBRD Blue Ribbon Investment Readiness &amp; Transaction Advisory</t>
+  </si>
+  <si>
+    <t>UNCDF</t>
+  </si>
+  <si>
+    <t>British International Investment</t>
+  </si>
+  <si>
+    <t>Building the Market for Blue Finance</t>
+  </si>
+  <si>
+    <t>Sanjoy Sanjal</t>
+  </si>
+  <si>
+    <t>Water.org</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Assessing the Relevance of Climate Resilience in 
+Water Supply and Sanitation (WSS) Business Loan Portfolios Across 
+Water.org’s Financial Institution Partners</t>
   </si>
 </sst>
 </file>
@@ -3907,7 +4047,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -4318,6 +4458,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="-0.24994659260841701"/>
+      </left>
+      <right style="thin">
+        <color theme="9" tint="-0.24994659260841701"/>
+      </right>
+      <top style="thin">
+        <color theme="9" tint="-0.24994659260841701"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9" tint="-0.24994659260841701"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -4365,7 +4520,7 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="147">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -4774,18 +4929,21 @@
     <xf numFmtId="14" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="20" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="16" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="4" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -4797,6 +4955,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="165" fontId="20" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -5748,7 +5909,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D008F4A-4F7B-4D00-B2B1-5D1E4C2AF094}">
-  <dimension ref="A1:V65"/>
+  <dimension ref="A1:V70"/>
   <sheetFormatPr defaultColWidth="47.54296875" defaultRowHeight="13" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.36328125" style="53" customWidth="1"/>
@@ -9206,50 +9367,50 @@
       <c r="C61" s="128" t="s">
         <v>87</v>
       </c>
-      <c r="D61" s="143" t="s">
+      <c r="D61" s="144" t="s">
         <v>55</v>
       </c>
-      <c r="E61" s="143" t="s">
+      <c r="E61" s="144" t="s">
         <v>562</v>
       </c>
-      <c r="F61" s="144" t="s">
+      <c r="F61" s="145" t="s">
         <v>940</v>
       </c>
-      <c r="G61" s="143" t="s">
+      <c r="G61" s="144" t="s">
         <v>79</v>
       </c>
-      <c r="H61" s="143" t="s">
+      <c r="H61" s="144" t="s">
         <v>22</v>
       </c>
-      <c r="I61" s="143" t="s">
+      <c r="I61" s="144" t="s">
         <v>23</v>
       </c>
-      <c r="J61" s="143" t="s">
+      <c r="J61" s="144" t="s">
         <v>24</v>
       </c>
-      <c r="K61" s="143" t="s">
+      <c r="K61" s="144" t="s">
         <v>25</v>
       </c>
-      <c r="L61" s="143"/>
-      <c r="M61" s="145">
+      <c r="L61" s="144"/>
+      <c r="M61" s="146">
         <v>46182</v>
       </c>
-      <c r="N61" s="143" t="s">
+      <c r="N61" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="O61" s="143"/>
-      <c r="P61" s="143"/>
-      <c r="Q61" s="143" t="s">
+      <c r="O61" s="144"/>
+      <c r="P61" s="144"/>
+      <c r="Q61" s="144" t="s">
         <v>568</v>
       </c>
-      <c r="R61" s="143" t="s">
+      <c r="R61" s="144" t="s">
         <v>53</v>
       </c>
-      <c r="S61" s="143" t="s">
+      <c r="S61" s="144" t="s">
         <v>41</v>
       </c>
-      <c r="T61" s="143"/>
-      <c r="U61" s="143"/>
+      <c r="T61" s="144"/>
+      <c r="U61" s="144"/>
     </row>
     <row r="62" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="121">
@@ -9265,10 +9426,10 @@
         <v>112</v>
       </c>
       <c r="E62" s="135" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="F62" s="136" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="G62" s="135" t="s">
         <v>34</v>
@@ -9286,7 +9447,7 @@
         <v>25</v>
       </c>
       <c r="L62" s="135"/>
-      <c r="M62" s="146"/>
+      <c r="M62" s="147"/>
       <c r="N62" s="135" t="s">
         <v>962</v>
       </c>
@@ -9345,7 +9506,7 @@
         <v>85</v>
       </c>
       <c r="L63" s="135"/>
-      <c r="M63" s="146"/>
+      <c r="M63" s="147"/>
       <c r="N63" s="135" t="s">
         <v>962</v>
       </c>
@@ -9380,7 +9541,7 @@
         <v>42</v>
       </c>
       <c r="F64" s="136" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="G64" s="135" t="s">
         <v>590</v>
@@ -9392,13 +9553,13 @@
         <v>23</v>
       </c>
       <c r="J64" s="135" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="K64" s="135" t="s">
         <v>25</v>
       </c>
       <c r="L64" s="135"/>
-      <c r="M64" s="146"/>
+      <c r="M64" s="147"/>
       <c r="N64" s="135" t="s">
         <v>47</v>
       </c>
@@ -9411,7 +9572,9 @@
       <c r="S64" s="135" t="s">
         <v>523</v>
       </c>
-      <c r="T64" s="135"/>
+      <c r="T64" s="135" t="s">
+        <v>49</v>
+      </c>
       <c r="U64" s="135">
         <v>4</v>
       </c>
@@ -9433,7 +9596,7 @@
         <v>20</v>
       </c>
       <c r="F65" s="136" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="G65" s="135" t="s">
         <v>34</v>
@@ -9451,7 +9614,7 @@
         <v>58</v>
       </c>
       <c r="L65" s="135"/>
-      <c r="M65" s="146">
+      <c r="M65" s="147">
         <v>46198</v>
       </c>
       <c r="N65" s="135" t="s">
@@ -9464,7 +9627,7 @@
         <v>46</v>
       </c>
       <c r="Q65" s="135" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="R65" s="135" t="s">
         <v>36</v>
@@ -9476,16 +9639,307 @@
         <v>95</v>
       </c>
       <c r="U65" s="135"/>
+    </row>
+    <row r="66" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="121">
+        <v>65</v>
+      </c>
+      <c r="B66" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C66" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D66" s="135"/>
+      <c r="E66" s="135"/>
+      <c r="F66" s="136" t="s">
+        <v>996</v>
+      </c>
+      <c r="G66" s="135" t="s">
+        <v>590</v>
+      </c>
+      <c r="H66" s="135" t="s">
+        <v>526</v>
+      </c>
+      <c r="I66" s="135" t="s">
+        <v>23</v>
+      </c>
+      <c r="J66" s="135" t="s">
+        <v>106</v>
+      </c>
+      <c r="K66" s="135" t="s">
+        <v>58</v>
+      </c>
+      <c r="L66" s="135"/>
+      <c r="M66" s="147">
+        <v>46202</v>
+      </c>
+      <c r="N66" s="135" t="s">
+        <v>962</v>
+      </c>
+      <c r="O66" s="135"/>
+      <c r="P66" s="135" t="s">
+        <v>523</v>
+      </c>
+      <c r="Q66" s="135"/>
+      <c r="R66" s="135" t="s">
+        <v>962</v>
+      </c>
+      <c r="S66" s="135" t="s">
+        <v>523</v>
+      </c>
+      <c r="T66" s="135" t="s">
+        <v>49</v>
+      </c>
+      <c r="U66" s="135">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="121">
+        <v>66</v>
+      </c>
+      <c r="B67" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C67" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D67" s="135" t="s">
+        <v>112</v>
+      </c>
+      <c r="E67" s="135" t="s">
+        <v>997</v>
+      </c>
+      <c r="F67" s="136" t="s">
+        <v>998</v>
+      </c>
+      <c r="G67" s="135" t="s">
+        <v>612</v>
+      </c>
+      <c r="H67" s="135" t="s">
+        <v>80</v>
+      </c>
+      <c r="I67" s="135" t="s">
+        <v>23</v>
+      </c>
+      <c r="J67" s="135" t="s">
+        <v>116</v>
+      </c>
+      <c r="K67" s="135"/>
+      <c r="L67" s="135"/>
+      <c r="M67" s="147">
+        <v>46201</v>
+      </c>
+      <c r="N67" s="135" t="s">
+        <v>60</v>
+      </c>
+      <c r="O67" s="135" t="s">
+        <v>89</v>
+      </c>
+      <c r="P67" s="135"/>
+      <c r="Q67" s="135" t="s">
+        <v>117</v>
+      </c>
+      <c r="R67" s="135" t="s">
+        <v>89</v>
+      </c>
+      <c r="S67" s="135" t="s">
+        <v>82</v>
+      </c>
+      <c r="T67" s="135" t="s">
+        <v>49</v>
+      </c>
+      <c r="U67" s="135">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="121">
+        <v>67</v>
+      </c>
+      <c r="B68" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C68" s="128" t="s">
+        <v>87</v>
+      </c>
+      <c r="D68" s="135" t="s">
+        <v>55</v>
+      </c>
+      <c r="E68" s="135" t="s">
+        <v>999</v>
+      </c>
+      <c r="F68" s="136" t="s">
+        <v>1000</v>
+      </c>
+      <c r="G68" s="135" t="s">
+        <v>612</v>
+      </c>
+      <c r="H68" s="135" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="135" t="s">
+        <v>23</v>
+      </c>
+      <c r="J68" s="135" t="s">
+        <v>701</v>
+      </c>
+      <c r="K68" s="135" t="s">
+        <v>25</v>
+      </c>
+      <c r="L68" s="135"/>
+      <c r="M68" s="147">
+        <v>46212</v>
+      </c>
+      <c r="N68" s="135" t="s">
+        <v>506</v>
+      </c>
+      <c r="O68" s="135"/>
+      <c r="P68" s="135"/>
+      <c r="Q68" s="135"/>
+      <c r="R68" s="135" t="s">
+        <v>61</v>
+      </c>
+      <c r="S68" s="135" t="s">
+        <v>41</v>
+      </c>
+      <c r="T68" s="135" t="s">
+        <v>95</v>
+      </c>
+      <c r="U68" s="135">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="121">
+        <v>68</v>
+      </c>
+      <c r="B69" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C69" s="148" t="s">
+        <v>681</v>
+      </c>
+      <c r="D69" s="135" t="s">
+        <v>1001</v>
+      </c>
+      <c r="E69" s="135" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F69" s="136" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G69" s="135" t="s">
+        <v>79</v>
+      </c>
+      <c r="H69" s="135" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I69" s="135" t="s">
+        <v>1005</v>
+      </c>
+      <c r="J69" s="135" t="s">
+        <v>1006</v>
+      </c>
+      <c r="K69" s="135" t="s">
+        <v>1007</v>
+      </c>
+      <c r="L69" s="135"/>
+      <c r="M69" s="147">
+        <v>46212</v>
+      </c>
+      <c r="N69" s="135" t="s">
+        <v>47</v>
+      </c>
+      <c r="O69" s="135" t="s">
+        <v>78</v>
+      </c>
+      <c r="P69" s="135"/>
+      <c r="Q69" s="135" t="s">
+        <v>1008</v>
+      </c>
+      <c r="R69" s="135" t="s">
+        <v>1009</v>
+      </c>
+      <c r="S69" s="135" t="s">
+        <v>78</v>
+      </c>
+      <c r="T69" s="135" t="s">
+        <v>1010</v>
+      </c>
+      <c r="U69" s="135"/>
+    </row>
+    <row r="70" spans="1:21" ht="13" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="121">
+        <v>69</v>
+      </c>
+      <c r="B70" s="126">
+        <v>2026</v>
+      </c>
+      <c r="C70" s="148" t="s">
+        <v>681</v>
+      </c>
+      <c r="D70" s="135" t="s">
+        <v>55</v>
+      </c>
+      <c r="E70" s="135" t="s">
+        <v>1011</v>
+      </c>
+      <c r="F70" s="136" t="s">
+        <v>1012</v>
+      </c>
+      <c r="G70" s="135" t="s">
+        <v>79</v>
+      </c>
+      <c r="H70" s="135" t="s">
+        <v>526</v>
+      </c>
+      <c r="I70" s="135" t="s">
+        <v>1005</v>
+      </c>
+      <c r="J70" s="135" t="s">
+        <v>24</v>
+      </c>
+      <c r="K70" s="135" t="s">
+        <v>25</v>
+      </c>
+      <c r="L70" s="135"/>
+      <c r="M70" s="147">
+        <v>46209</v>
+      </c>
+      <c r="N70" s="135" t="s">
+        <v>1009</v>
+      </c>
+      <c r="O70" s="135"/>
+      <c r="P70" s="135" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q70" s="135" t="s">
+        <v>1013</v>
+      </c>
+      <c r="R70" s="135" t="s">
+        <v>1009</v>
+      </c>
+      <c r="S70" s="135" t="s">
+        <v>28</v>
+      </c>
+      <c r="T70" s="135" t="s">
+        <v>49</v>
+      </c>
+      <c r="U70" s="135">
+        <v>3</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:V57" xr:uid="{0D008F4A-4F7B-4D00-B2B1-5D1E4C2AF094}"/>
   <phoneticPr fontId="42" type="noConversion"/>
   <dataValidations count="7">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="U1 U49:U61 U66:U1048576 M49:M61 M66:M1048576" xr:uid="{53C03EB9-171C-49BE-A2B1-76486CCC2F4C}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M49:M1048576 U49:U1048576 U1" xr:uid="{53C03EB9-171C-49BE-A2B1-76486CCC2F4C}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="It should be in months" sqref="U2:U26 V1 U28:U56 U58:U61 V66:V1048576" xr:uid="{AC6A3088-3943-48BB-8581-3772A4F7A436}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="It should be in months" sqref="U2:U26 V1 U28:U56 U58:U70 V71:V1048576" xr:uid="{AC6A3088-3943-48BB-8581-3772A4F7A436}">
       <formula1>1</formula1>
       <formula2>60</formula2>
     </dataValidation>
@@ -9517,7 +9971,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F7F4377-AB0D-4AD1-9A42-D0995505B602}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:W217"/>
+  <dimension ref="A1:W229"/>
   <sheetFormatPr defaultRowHeight="10" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="8.81640625" style="53" bestFit="1" customWidth="1"/>
@@ -9525,7 +9979,7 @@
     <col min="4" max="11" width="8.7265625" style="53"/>
     <col min="12" max="12" width="21.1796875" style="42" customWidth="1"/>
     <col min="13" max="19" width="8.7265625" style="53"/>
-    <col min="20" max="20" width="9" style="53" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="11.7265625" style="53" customWidth="1"/>
     <col min="21" max="21" width="8.7265625" style="53"/>
     <col min="22" max="23" width="8.81640625" style="53" bestFit="1" customWidth="1"/>
     <col min="24" max="16384" width="8.7265625" style="53"/>
@@ -15549,7 +16003,7 @@
       <c r="V96" s="36"/>
     </row>
     <row r="97" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="36">
+      <c r="A97" s="102">
         <v>1</v>
       </c>
       <c r="B97" s="51">
@@ -15604,7 +16058,7 @@
       </c>
     </row>
     <row r="98" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="36">
+      <c r="A98" s="102">
         <v>2</v>
       </c>
       <c r="B98" s="51">
@@ -15671,7 +16125,7 @@
       </c>
     </row>
     <row r="99" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="36">
+      <c r="A99" s="102">
         <v>3</v>
       </c>
       <c r="B99" s="51">
@@ -15738,7 +16192,7 @@
       </c>
     </row>
     <row r="100" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="36">
+      <c r="A100" s="102">
         <v>4</v>
       </c>
       <c r="B100" s="51">
@@ -15805,7 +16259,7 @@
       </c>
     </row>
     <row r="101" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="36">
+      <c r="A101" s="102">
         <v>5</v>
       </c>
       <c r="B101" s="51">
@@ -15866,7 +16320,7 @@
       </c>
     </row>
     <row r="102" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="36">
+      <c r="A102" s="102">
         <v>6</v>
       </c>
       <c r="B102" s="51">
@@ -15931,7 +16385,7 @@
       </c>
     </row>
     <row r="103" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="36">
+      <c r="A103" s="102">
         <v>7</v>
       </c>
       <c r="B103" s="51">
@@ -15994,7 +16448,7 @@
       <c r="W103" s="36"/>
     </row>
     <row r="104" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="36">
+      <c r="A104" s="102">
         <v>8</v>
       </c>
       <c r="B104" s="51">
@@ -16061,7 +16515,7 @@
       </c>
     </row>
     <row r="105" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="36">
+      <c r="A105" s="102">
         <v>9</v>
       </c>
       <c r="B105" s="51">
@@ -16126,7 +16580,7 @@
       </c>
     </row>
     <row r="106" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="36">
+      <c r="A106" s="102">
         <v>10</v>
       </c>
       <c r="B106" s="51">
@@ -16191,7 +16645,7 @@
       </c>
     </row>
     <row r="107" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="36">
+      <c r="A107" s="102">
         <v>11</v>
       </c>
       <c r="B107" s="51">
@@ -16256,7 +16710,7 @@
       </c>
     </row>
     <row r="108" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="36">
+      <c r="A108" s="102">
         <v>12</v>
       </c>
       <c r="B108" s="51">
@@ -16321,7 +16775,7 @@
       </c>
     </row>
     <row r="109" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="38">
+      <c r="A109" s="102">
         <v>13</v>
       </c>
       <c r="B109" s="51">
@@ -16386,7 +16840,7 @@
       </c>
     </row>
     <row r="110" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="36">
+      <c r="A110" s="102">
         <v>14</v>
       </c>
       <c r="B110" s="51">
@@ -16441,7 +16895,7 @@
       <c r="W110" s="36"/>
     </row>
     <row r="111" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="36">
+      <c r="A111" s="102">
         <v>15</v>
       </c>
       <c r="B111" s="51">
@@ -16498,7 +16952,7 @@
       <c r="W111" s="36"/>
     </row>
     <row r="112" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="36">
+      <c r="A112" s="102">
         <v>16</v>
       </c>
       <c r="B112" s="51">
@@ -16565,7 +17019,7 @@
       </c>
     </row>
     <row r="113" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="36">
+      <c r="A113" s="102">
         <v>17</v>
       </c>
       <c r="B113" s="51">
@@ -16628,7 +17082,7 @@
       </c>
     </row>
     <row r="114" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="36">
+      <c r="A114" s="102">
         <v>18</v>
       </c>
       <c r="B114" s="51">
@@ -16695,7 +17149,7 @@
       </c>
     </row>
     <row r="115" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="36">
+      <c r="A115" s="102">
         <v>19</v>
       </c>
       <c r="B115" s="51">
@@ -16764,7 +17218,7 @@
       </c>
     </row>
     <row r="116" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="36">
+      <c r="A116" s="102">
         <v>20</v>
       </c>
       <c r="B116" s="51">
@@ -16829,7 +17283,7 @@
       </c>
     </row>
     <row r="117" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="36">
+      <c r="A117" s="102">
         <v>21</v>
       </c>
       <c r="B117" s="51">
@@ -16896,7 +17350,7 @@
       </c>
     </row>
     <row r="118" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="36">
+      <c r="A118" s="102">
         <v>22</v>
       </c>
       <c r="B118" s="51">
@@ -16959,7 +17413,7 @@
       <c r="W118" s="36"/>
     </row>
     <row r="119" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="36">
+      <c r="A119" s="102">
         <v>23</v>
       </c>
       <c r="B119" s="51">
@@ -17026,7 +17480,7 @@
       </c>
     </row>
     <row r="120" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="36">
+      <c r="A120" s="102">
         <v>24</v>
       </c>
       <c r="B120" s="51">
@@ -17091,7 +17545,7 @@
       </c>
     </row>
     <row r="121" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="36">
+      <c r="A121" s="102">
         <v>25</v>
       </c>
       <c r="B121" s="51">
@@ -17158,7 +17612,7 @@
       </c>
     </row>
     <row r="122" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="36">
+      <c r="A122" s="102">
         <v>26</v>
       </c>
       <c r="B122" s="51">
@@ -17221,7 +17675,7 @@
       <c r="W122" s="36"/>
     </row>
     <row r="123" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="36">
+      <c r="A123" s="102">
         <v>27</v>
       </c>
       <c r="B123" s="51">
@@ -17288,7 +17742,7 @@
       </c>
     </row>
     <row r="124" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="36">
+      <c r="A124" s="102">
         <v>28</v>
       </c>
       <c r="B124" s="51">
@@ -17353,7 +17807,7 @@
       </c>
     </row>
     <row r="125" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="36">
+      <c r="A125" s="102">
         <v>29</v>
       </c>
       <c r="B125" s="51">
@@ -17408,7 +17862,7 @@
       <c r="W125" s="36"/>
     </row>
     <row r="126" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="36">
+      <c r="A126" s="102">
         <v>30</v>
       </c>
       <c r="B126" s="51">
@@ -17473,7 +17927,7 @@
       </c>
     </row>
     <row r="127" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="36">
+      <c r="A127" s="102">
         <v>31</v>
       </c>
       <c r="B127" s="51">
@@ -17534,7 +17988,7 @@
       </c>
     </row>
     <row r="128" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="36">
+      <c r="A128" s="102">
         <v>32</v>
       </c>
       <c r="B128" s="51">
@@ -17587,7 +18041,7 @@
       <c r="W128" s="36"/>
     </row>
     <row r="129" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="139">
+      <c r="A129" s="102">
         <v>33</v>
       </c>
       <c r="B129" s="51">
@@ -17646,7 +18100,7 @@
       </c>
     </row>
     <row r="130" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="138">
+      <c r="A130" s="102">
         <v>34</v>
       </c>
       <c r="B130" s="51">
@@ -17707,7 +18161,7 @@
       </c>
     </row>
     <row r="131" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="138">
+      <c r="A131" s="102">
         <v>35</v>
       </c>
       <c r="B131" s="51">
@@ -17776,7 +18230,7 @@
       </c>
     </row>
     <row r="132" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="138">
+      <c r="A132" s="102">
         <v>36</v>
       </c>
       <c r="B132" s="51">
@@ -17841,7 +18295,7 @@
       </c>
     </row>
     <row r="133" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="138">
+      <c r="A133" s="102">
         <v>37</v>
       </c>
       <c r="B133" s="51">
@@ -17908,7 +18362,7 @@
       </c>
     </row>
     <row r="134" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="138">
+      <c r="A134" s="102">
         <v>38</v>
       </c>
       <c r="B134" s="51">
@@ -17979,8 +18433,8 @@
       </c>
     </row>
     <row r="135" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="138">
-        <v>38</v>
+      <c r="A135" s="102">
+        <v>39</v>
       </c>
       <c r="B135" s="51">
         <v>2026</v>
@@ -18046,8 +18500,8 @@
       </c>
     </row>
     <row r="136" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="138">
-        <v>39</v>
+      <c r="A136" s="102">
+        <v>40</v>
       </c>
       <c r="B136" s="51">
         <v>2026</v>
@@ -18111,8 +18565,8 @@
       </c>
     </row>
     <row r="137" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="138">
-        <v>40</v>
+      <c r="A137" s="102">
+        <v>41</v>
       </c>
       <c r="B137" s="51">
         <v>2026</v>
@@ -18172,8 +18626,8 @@
       <c r="W137" s="36"/>
     </row>
     <row r="138" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="138">
-        <v>41</v>
+      <c r="A138" s="121">
+        <v>42</v>
       </c>
       <c r="B138" s="51">
         <v>2026</v>
@@ -18237,8 +18691,8 @@
       <c r="W138" s="36"/>
     </row>
     <row r="139" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="138">
-        <v>42</v>
+      <c r="A139" s="121">
+        <v>43</v>
       </c>
       <c r="B139" s="51">
         <v>2026</v>
@@ -18246,1574 +18700,2534 @@
       <c r="C139" s="117" t="s">
         <v>87</v>
       </c>
-      <c r="D139" s="36" t="s">
+      <c r="D139" s="51" t="s">
         <v>55</v>
       </c>
-      <c r="E139" s="36" t="s">
+      <c r="E139" s="51" t="s">
         <v>546</v>
       </c>
-      <c r="F139" s="36" t="s">
+      <c r="F139" s="51" t="s">
         <v>619</v>
       </c>
-      <c r="G139" s="36" t="s">
+      <c r="G139" s="51" t="s">
         <v>79</v>
       </c>
-      <c r="H139" s="36" t="s">
+      <c r="H139" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="I139" s="36" t="s">
+      <c r="I139" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="J139" s="36" t="s">
+      <c r="J139" s="51" t="s">
         <v>620</v>
       </c>
-      <c r="K139" s="36" t="s">
+      <c r="K139" s="51" t="s">
         <v>25</v>
       </c>
-      <c r="L139" s="37">
+      <c r="L139" s="139">
         <v>46148</v>
       </c>
-      <c r="M139" s="36" t="s">
+      <c r="M139" s="51" t="s">
         <v>621</v>
       </c>
-      <c r="N139" s="36" t="s">
+      <c r="N139" s="51" t="s">
         <v>59</v>
       </c>
-      <c r="O139" s="36" t="s">
+      <c r="O139" s="51" t="s">
         <v>47</v>
       </c>
-      <c r="P139" s="36"/>
-      <c r="Q139" s="36"/>
-      <c r="R139" s="36" t="s">
+      <c r="P139" s="51"/>
+      <c r="Q139" s="51"/>
+      <c r="R139" s="51" t="s">
         <v>67</v>
       </c>
-      <c r="S139" s="36" t="s">
+      <c r="S139" s="51" t="s">
         <v>54</v>
       </c>
-      <c r="T139" s="52">
+      <c r="T139" s="69">
         <v>1500000</v>
       </c>
-      <c r="U139" s="36" t="s">
+      <c r="U139" s="51" t="s">
         <v>49</v>
       </c>
-      <c r="V139" s="37"/>
-      <c r="W139" s="36">
+      <c r="V139" s="139"/>
+      <c r="W139" s="51">
         <v>24</v>
       </c>
     </row>
     <row r="140" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="138">
+      <c r="A140" s="121">
+        <v>44</v>
+      </c>
+      <c r="B140" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C140" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D140" s="142" t="s">
+        <v>83</v>
+      </c>
+      <c r="E140" s="142" t="s">
+        <v>550</v>
+      </c>
+      <c r="F140" s="142" t="s">
+        <v>622</v>
+      </c>
+      <c r="G140" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H140" s="142" t="s">
+        <v>526</v>
+      </c>
+      <c r="I140" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J140" s="142" t="s">
+        <v>24</v>
+      </c>
+      <c r="K140" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L140" s="143">
+        <v>46141</v>
+      </c>
+      <c r="M140" s="142" t="s">
         <v>43</v>
       </c>
-      <c r="B140" s="51">
+      <c r="N140" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="O140" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="P140" s="142"/>
+      <c r="Q140" s="142"/>
+      <c r="R140" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="S140" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T140" s="142">
+        <v>37304</v>
+      </c>
+      <c r="U140" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V140" s="142"/>
+      <c r="W140" s="142"/>
+    </row>
+    <row r="141" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="121">
+        <v>45</v>
+      </c>
+      <c r="B141" s="140">
         <v>2026</v>
       </c>
-      <c r="C140" s="117" t="s">
+      <c r="C141" s="141" t="s">
         <v>87</v>
       </c>
-      <c r="D140" s="53" t="s">
+      <c r="D141" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E141" s="142" t="s">
+        <v>623</v>
+      </c>
+      <c r="F141" s="142" t="s">
+        <v>597</v>
+      </c>
+      <c r="G141" s="142" t="s">
+        <v>79</v>
+      </c>
+      <c r="H141" s="142" t="s">
+        <v>40</v>
+      </c>
+      <c r="I141" s="142" t="s">
+        <v>104</v>
+      </c>
+      <c r="J141" s="142" t="s">
+        <v>624</v>
+      </c>
+      <c r="K141" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L141" s="143">
+        <v>46139</v>
+      </c>
+      <c r="M141" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="N141" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="O141" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="P141" s="142" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q141" s="142"/>
+      <c r="R141" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="S141" s="142" t="s">
+        <v>28</v>
+      </c>
+      <c r="T141" s="142">
+        <v>904783.35999999999</v>
+      </c>
+      <c r="U141" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V141" s="142"/>
+      <c r="W141" s="142">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="121">
+        <v>46</v>
+      </c>
+      <c r="B142" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C142" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D142" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E142" s="142" t="s">
+        <v>779</v>
+      </c>
+      <c r="F142" s="142" t="s">
+        <v>951</v>
+      </c>
+      <c r="G142" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H142" s="142" t="s">
+        <v>51</v>
+      </c>
+      <c r="I142" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J142" s="142" t="s">
+        <v>24</v>
+      </c>
+      <c r="K142" s="142" t="s">
+        <v>77</v>
+      </c>
+      <c r="L142" s="143">
+        <v>46149</v>
+      </c>
+      <c r="M142" s="142" t="s">
+        <v>109</v>
+      </c>
+      <c r="N142" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="O142" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="P142" s="142"/>
+      <c r="Q142" s="142" t="s">
+        <v>952</v>
+      </c>
+      <c r="R142" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="S142" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T142" s="142">
+        <v>213955</v>
+      </c>
+      <c r="U142" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V142" s="142"/>
+      <c r="W142" s="142"/>
+    </row>
+    <row r="143" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="121">
+        <v>47</v>
+      </c>
+      <c r="B143" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C143" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D143" s="142" t="s">
         <v>83</v>
       </c>
-      <c r="E140" s="53" t="s">
-        <v>550</v>
-      </c>
-      <c r="F140" s="53" t="s">
-        <v>622</v>
-      </c>
-      <c r="G140" s="53" t="s">
+      <c r="E143" s="142" t="s">
+        <v>592</v>
+      </c>
+      <c r="F143" s="142" t="s">
+        <v>953</v>
+      </c>
+      <c r="G143" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="H140" s="53" t="s">
+      <c r="H143" s="142" t="s">
+        <v>51</v>
+      </c>
+      <c r="I143" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J143" s="142" t="s">
+        <v>24</v>
+      </c>
+      <c r="K143" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L143" s="143">
+        <v>46153</v>
+      </c>
+      <c r="M143" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="N143" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="O143" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="P143" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q143" s="142" t="s">
+        <v>954</v>
+      </c>
+      <c r="R143" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="S143" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T143" s="142">
+        <v>47777.97</v>
+      </c>
+      <c r="U143" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V143" s="142"/>
+      <c r="W143" s="142">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="121">
+        <v>48</v>
+      </c>
+      <c r="B144" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C144" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D144" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E144" s="142" t="s">
+        <v>955</v>
+      </c>
+      <c r="F144" s="142" t="s">
+        <v>956</v>
+      </c>
+      <c r="G144" s="142" t="s">
+        <v>79</v>
+      </c>
+      <c r="H144" s="142" t="s">
+        <v>51</v>
+      </c>
+      <c r="I144" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J144" s="142" t="s">
+        <v>116</v>
+      </c>
+      <c r="K144" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L144" s="143">
+        <v>46154</v>
+      </c>
+      <c r="M144" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="N144" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="O144" s="142"/>
+      <c r="P144" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q144" s="142" t="s">
+        <v>117</v>
+      </c>
+      <c r="R144" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="S144" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="T144" s="142">
+        <v>18445</v>
+      </c>
+      <c r="U144" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V144" s="142"/>
+      <c r="W144" s="142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="121">
+        <v>49</v>
+      </c>
+      <c r="B145" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C145" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D145" s="142" t="s">
+        <v>63</v>
+      </c>
+      <c r="E145" s="142" t="s">
+        <v>957</v>
+      </c>
+      <c r="F145" s="142" t="s">
+        <v>958</v>
+      </c>
+      <c r="G145" s="142" t="s">
+        <v>34</v>
+      </c>
+      <c r="H145" s="142" t="s">
+        <v>51</v>
+      </c>
+      <c r="I145" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J145" s="142" t="s">
+        <v>24</v>
+      </c>
+      <c r="K145" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="L145" s="143"/>
+      <c r="M145" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="N145" s="142"/>
+      <c r="O145" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="P145" s="142"/>
+      <c r="Q145" s="142"/>
+      <c r="R145" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="S145" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="T145" s="142"/>
+      <c r="U145" s="142" t="s">
+        <v>95</v>
+      </c>
+      <c r="V145" s="142"/>
+      <c r="W145" s="142"/>
+    </row>
+    <row r="146" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="121">
+        <v>50</v>
+      </c>
+      <c r="B146" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C146" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D146" s="142" t="s">
+        <v>959</v>
+      </c>
+      <c r="E146" s="142" t="s">
+        <v>960</v>
+      </c>
+      <c r="F146" s="142" t="s">
+        <v>961</v>
+      </c>
+      <c r="G146" s="142"/>
+      <c r="H146" s="142" t="s">
+        <v>80</v>
+      </c>
+      <c r="I146" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J146" s="142" t="s">
+        <v>106</v>
+      </c>
+      <c r="K146" s="142" t="s">
+        <v>85</v>
+      </c>
+      <c r="L146" s="143">
+        <v>46162</v>
+      </c>
+      <c r="M146" s="142" t="s">
+        <v>962</v>
+      </c>
+      <c r="N146" s="142"/>
+      <c r="O146" s="142"/>
+      <c r="P146" s="142"/>
+      <c r="Q146" s="142" t="s">
+        <v>899</v>
+      </c>
+      <c r="R146" s="142" t="s">
+        <v>523</v>
+      </c>
+      <c r="S146" s="142" t="s">
+        <v>78</v>
+      </c>
+      <c r="T146" s="142"/>
+      <c r="U146" s="142" t="s">
+        <v>95</v>
+      </c>
+      <c r="V146" s="142"/>
+      <c r="W146" s="142"/>
+    </row>
+    <row r="147" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="121">
+        <v>51</v>
+      </c>
+      <c r="B147" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C147" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D147" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E147" s="142" t="s">
+        <v>546</v>
+      </c>
+      <c r="F147" s="142" t="s">
+        <v>963</v>
+      </c>
+      <c r="G147" s="142" t="s">
+        <v>508</v>
+      </c>
+      <c r="H147" s="142" t="s">
+        <v>40</v>
+      </c>
+      <c r="I147" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J147" s="142" t="s">
+        <v>106</v>
+      </c>
+      <c r="K147" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L147" s="143">
+        <v>46165</v>
+      </c>
+      <c r="M147" s="142" t="s">
+        <v>962</v>
+      </c>
+      <c r="N147" s="142" t="s">
+        <v>523</v>
+      </c>
+      <c r="O147" s="142" t="s">
+        <v>78</v>
+      </c>
+      <c r="P147" s="142"/>
+      <c r="Q147" s="142" t="s">
+        <v>899</v>
+      </c>
+      <c r="R147" s="142" t="s">
+        <v>523</v>
+      </c>
+      <c r="S147" s="142" t="s">
+        <v>78</v>
+      </c>
+      <c r="T147" s="142">
+        <v>60000</v>
+      </c>
+      <c r="U147" s="142" t="s">
+        <v>95</v>
+      </c>
+      <c r="V147" s="142"/>
+      <c r="W147" s="142"/>
+    </row>
+    <row r="148" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="121">
+        <v>52</v>
+      </c>
+      <c r="B148" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C148" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D148" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E148" s="142" t="s">
+        <v>779</v>
+      </c>
+      <c r="F148" s="142" t="s">
+        <v>964</v>
+      </c>
+      <c r="G148" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H148" s="142" t="s">
+        <v>40</v>
+      </c>
+      <c r="I148" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J148" s="142" t="s">
+        <v>24</v>
+      </c>
+      <c r="K148" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L148" s="143">
+        <v>46167</v>
+      </c>
+      <c r="M148" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="N148" s="142" t="s">
+        <v>53</v>
+      </c>
+      <c r="O148" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="P148" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q148" s="142" t="s">
+        <v>965</v>
+      </c>
+      <c r="R148" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="S148" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T148" s="142">
+        <v>137528</v>
+      </c>
+      <c r="U148" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V148" s="142"/>
+      <c r="W148" s="142">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="121">
+        <v>53</v>
+      </c>
+      <c r="B149" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C149" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D149" s="142" t="s">
+        <v>19</v>
+      </c>
+      <c r="E149" s="142" t="s">
+        <v>42</v>
+      </c>
+      <c r="F149" s="142" t="s">
+        <v>966</v>
+      </c>
+      <c r="G149" s="142"/>
+      <c r="H149" s="142" t="s">
+        <v>44</v>
+      </c>
+      <c r="I149" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J149" s="142" t="s">
+        <v>88</v>
+      </c>
+      <c r="K149" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="L149" s="143">
+        <v>46156</v>
+      </c>
+      <c r="M149" s="142" t="s">
+        <v>89</v>
+      </c>
+      <c r="N149" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="O149" s="142" t="s">
+        <v>90</v>
+      </c>
+      <c r="P149" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q149" s="142" t="s">
+        <v>967</v>
+      </c>
+      <c r="R149" s="142" t="s">
+        <v>89</v>
+      </c>
+      <c r="S149" s="142" t="s">
+        <v>113</v>
+      </c>
+      <c r="T149" s="142">
+        <v>87726.85</v>
+      </c>
+      <c r="U149" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V149" s="142"/>
+      <c r="W149" s="142">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="121">
+        <v>54</v>
+      </c>
+      <c r="B150" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C150" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D150" s="142" t="s">
+        <v>517</v>
+      </c>
+      <c r="E150" s="142" t="s">
+        <v>853</v>
+      </c>
+      <c r="F150" s="142" t="s">
+        <v>968</v>
+      </c>
+      <c r="G150" s="142" t="s">
+        <v>56</v>
+      </c>
+      <c r="H150" s="142" t="s">
+        <v>22</v>
+      </c>
+      <c r="I150" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J150" s="142" t="s">
+        <v>881</v>
+      </c>
+      <c r="K150" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L150" s="143">
+        <v>46163</v>
+      </c>
+      <c r="M150" s="142" t="s">
+        <v>59</v>
+      </c>
+      <c r="N150" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="O150" s="142" t="s">
+        <v>969</v>
+      </c>
+      <c r="P150" s="142"/>
+      <c r="Q150" s="142"/>
+      <c r="R150" s="142" t="s">
+        <v>59</v>
+      </c>
+      <c r="S150" s="142" t="s">
+        <v>33</v>
+      </c>
+      <c r="T150" s="142">
+        <v>61684</v>
+      </c>
+      <c r="U150" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V150" s="142"/>
+      <c r="W150" s="142">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="121">
+        <v>55</v>
+      </c>
+      <c r="B151" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C151" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D151" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E151" s="142" t="s">
+        <v>970</v>
+      </c>
+      <c r="F151" s="142" t="s">
+        <v>971</v>
+      </c>
+      <c r="G151" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H151" s="142" t="s">
         <v>526</v>
       </c>
-      <c r="I140" s="53" t="s">
+      <c r="I151" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J151" s="142" t="s">
+        <v>24</v>
+      </c>
+      <c r="K151" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="L151" s="143">
+        <v>46160</v>
+      </c>
+      <c r="M151" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="N151" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="O151" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="P151" s="142" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q151" s="142" t="s">
+        <v>972</v>
+      </c>
+      <c r="R151" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="S151" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T151" s="142">
+        <v>78815</v>
+      </c>
+      <c r="U151" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V151" s="142"/>
+      <c r="W151" s="142"/>
+    </row>
+    <row r="152" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A152" s="121">
+        <v>56</v>
+      </c>
+      <c r="B152" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C152" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D152" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E152" s="142" t="s">
+        <v>64</v>
+      </c>
+      <c r="F152" s="142" t="s">
+        <v>973</v>
+      </c>
+      <c r="G152" s="142" t="s">
+        <v>50</v>
+      </c>
+      <c r="H152" s="142" t="s">
+        <v>51</v>
+      </c>
+      <c r="I152" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="J140" s="53" t="s">
+      <c r="J152" s="142" t="s">
+        <v>974</v>
+      </c>
+      <c r="K152" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L152" s="143">
+        <v>46167</v>
+      </c>
+      <c r="M152" s="142" t="s">
+        <v>53</v>
+      </c>
+      <c r="N152" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="O152" s="142" t="s">
+        <v>65</v>
+      </c>
+      <c r="P152" s="142"/>
+      <c r="Q152" s="142" t="s">
+        <v>975</v>
+      </c>
+      <c r="R152" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="S152" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="T152" s="142">
+        <v>122050.6</v>
+      </c>
+      <c r="U152" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V152" s="142"/>
+      <c r="W152" s="142">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A153" s="121">
+        <v>57</v>
+      </c>
+      <c r="B153" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C153" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D153" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E153" s="142" t="s">
+        <v>562</v>
+      </c>
+      <c r="F153" s="142" t="s">
+        <v>976</v>
+      </c>
+      <c r="G153" s="142" t="s">
+        <v>977</v>
+      </c>
+      <c r="H153" s="142" t="s">
+        <v>713</v>
+      </c>
+      <c r="I153" s="142" t="s">
+        <v>104</v>
+      </c>
+      <c r="J153" s="142" t="s">
+        <v>978</v>
+      </c>
+      <c r="K153" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L153" s="143">
+        <v>46176</v>
+      </c>
+      <c r="M153" s="142" t="s">
+        <v>506</v>
+      </c>
+      <c r="N153" s="142" t="s">
+        <v>621</v>
+      </c>
+      <c r="O153" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="P153" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q153" s="142" t="s">
+        <v>979</v>
+      </c>
+      <c r="R153" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="S153" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="T153" s="142">
+        <v>60166.16</v>
+      </c>
+      <c r="U153" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V153" s="142"/>
+      <c r="W153" s="142">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A154" s="121">
+        <v>58</v>
+      </c>
+      <c r="B154" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C154" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D154" s="142" t="s">
+        <v>83</v>
+      </c>
+      <c r="E154" s="142" t="s">
+        <v>980</v>
+      </c>
+      <c r="F154" s="142" t="s">
+        <v>981</v>
+      </c>
+      <c r="G154" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H154" s="142" t="s">
+        <v>44</v>
+      </c>
+      <c r="I154" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J154" s="142" t="s">
+        <v>978</v>
+      </c>
+      <c r="K154" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L154" s="143">
+        <v>46169</v>
+      </c>
+      <c r="M154" s="142" t="s">
+        <v>109</v>
+      </c>
+      <c r="N154" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="O154" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="P154" s="142"/>
+      <c r="Q154" s="142"/>
+      <c r="R154" s="142" t="s">
+        <v>109</v>
+      </c>
+      <c r="S154" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T154" s="142">
+        <v>33017.660000000003</v>
+      </c>
+      <c r="U154" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V154" s="142"/>
+      <c r="W154" s="142"/>
+    </row>
+    <row r="155" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A155" s="121">
+        <v>59</v>
+      </c>
+      <c r="B155" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C155" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D155" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E155" s="142" t="s">
+        <v>562</v>
+      </c>
+      <c r="F155" s="142" t="s">
+        <v>982</v>
+      </c>
+      <c r="G155" s="142" t="s">
+        <v>74</v>
+      </c>
+      <c r="H155" s="142" t="s">
+        <v>526</v>
+      </c>
+      <c r="I155" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J155" s="142" t="s">
+        <v>983</v>
+      </c>
+      <c r="K155" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L155" s="143">
+        <v>46185</v>
+      </c>
+      <c r="M155" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="N155" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="O155" s="142" t="s">
+        <v>89</v>
+      </c>
+      <c r="P155" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q155" s="142"/>
+      <c r="R155" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="S155" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T155" s="142"/>
+      <c r="U155" s="142" t="s">
+        <v>95</v>
+      </c>
+      <c r="V155" s="142"/>
+      <c r="W155" s="142">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="121">
+        <v>60</v>
+      </c>
+      <c r="B156" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C156" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D156" s="142" t="s">
+        <v>83</v>
+      </c>
+      <c r="E156" s="142" t="s">
+        <v>984</v>
+      </c>
+      <c r="F156" s="142" t="s">
+        <v>985</v>
+      </c>
+      <c r="G156" s="142"/>
+      <c r="H156" s="142"/>
+      <c r="I156" s="142"/>
+      <c r="J156" s="142"/>
+      <c r="K156" s="142" t="s">
+        <v>77</v>
+      </c>
+      <c r="L156" s="143">
+        <v>46171</v>
+      </c>
+      <c r="M156" s="142" t="s">
+        <v>506</v>
+      </c>
+      <c r="N156" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="O156" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="P156" s="142" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q156" s="142"/>
+      <c r="R156" s="142" t="s">
+        <v>59</v>
+      </c>
+      <c r="S156" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="T156" s="142">
+        <v>77099.490000000005</v>
+      </c>
+      <c r="U156" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V156" s="142"/>
+      <c r="W156" s="142"/>
+    </row>
+    <row r="157" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A157" s="121">
+        <v>61</v>
+      </c>
+      <c r="B157" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C157" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D157" s="142" t="s">
+        <v>799</v>
+      </c>
+      <c r="E157" s="142" t="s">
+        <v>509</v>
+      </c>
+      <c r="F157" s="142" t="s">
+        <v>986</v>
+      </c>
+      <c r="G157" s="142"/>
+      <c r="H157" s="142"/>
+      <c r="I157" s="142"/>
+      <c r="J157" s="142"/>
+      <c r="K157" s="142"/>
+      <c r="L157" s="143">
+        <v>46181</v>
+      </c>
+      <c r="M157" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="N157" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="O157" s="142" t="s">
+        <v>59</v>
+      </c>
+      <c r="P157" s="142" t="s">
+        <v>621</v>
+      </c>
+      <c r="Q157" s="142"/>
+      <c r="R157" s="142" t="s">
+        <v>538</v>
+      </c>
+      <c r="S157" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="T157" s="142">
+        <v>15000</v>
+      </c>
+      <c r="U157" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V157" s="142"/>
+      <c r="W157" s="142">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A158" s="121">
+        <v>62</v>
+      </c>
+      <c r="B158" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C158" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D158" s="142" t="s">
+        <v>30</v>
+      </c>
+      <c r="E158" s="142" t="s">
+        <v>987</v>
+      </c>
+      <c r="F158" s="142" t="s">
+        <v>988</v>
+      </c>
+      <c r="G158" s="142" t="s">
+        <v>508</v>
+      </c>
+      <c r="H158" s="142" t="s">
+        <v>22</v>
+      </c>
+      <c r="I158" s="142" t="s">
+        <v>104</v>
+      </c>
+      <c r="J158" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="K140" s="53" t="s">
+      <c r="K158" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="L140" s="42">
-        <v>46141</v>
-      </c>
-      <c r="M140" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="N140" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="O140" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="R140" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="S140" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="T140" s="53">
-        <v>37304</v>
-      </c>
-      <c r="U140" s="53" t="s">
+      <c r="L158" s="143">
+        <v>46178</v>
+      </c>
+      <c r="M158" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="N158" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="O158" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="P158" s="142"/>
+      <c r="Q158" s="142" t="s">
+        <v>989</v>
+      </c>
+      <c r="R158" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="S158" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="T158" s="142">
+        <v>167739.19</v>
+      </c>
+      <c r="U158" s="142" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="141" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="138">
+      <c r="V158" s="142"/>
+      <c r="W158" s="142">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="121">
+        <v>63</v>
+      </c>
+      <c r="B159" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C159" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D159" s="142" t="s">
+        <v>30</v>
+      </c>
+      <c r="E159" s="142" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F159" s="142" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G159" s="142" t="s">
+        <v>74</v>
+      </c>
+      <c r="H159" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="B141" s="51">
+      <c r="I159" s="142" t="s">
+        <v>104</v>
+      </c>
+      <c r="J159" s="142" t="s">
+        <v>24</v>
+      </c>
+      <c r="K159" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L159" s="143">
+        <v>46195</v>
+      </c>
+      <c r="M159" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="N159" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="O159" s="142" t="s">
+        <v>89</v>
+      </c>
+      <c r="P159" s="142"/>
+      <c r="Q159" s="142"/>
+      <c r="R159" s="142" t="s">
+        <v>60</v>
+      </c>
+      <c r="S159" s="142" t="s">
+        <v>28</v>
+      </c>
+      <c r="T159" s="142"/>
+      <c r="U159" s="142" t="s">
+        <v>95</v>
+      </c>
+      <c r="V159" s="142"/>
+      <c r="W159" s="142">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A160" s="121">
+        <v>64</v>
+      </c>
+      <c r="B160" s="140">
         <v>2026</v>
       </c>
-      <c r="C141" s="117" t="s">
+      <c r="C160" s="141" t="s">
         <v>87</v>
       </c>
-      <c r="D141" s="53" t="s">
+      <c r="D160" s="142" t="s">
         <v>55</v>
       </c>
-      <c r="E141" s="53" t="s">
-        <v>623</v>
-      </c>
-      <c r="F141" s="53" t="s">
-        <v>597</v>
-      </c>
-      <c r="G141" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="H141" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="I141" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="J141" s="53" t="s">
-        <v>624</v>
-      </c>
-      <c r="K141" s="53" t="s">
+      <c r="E160" s="142" t="s">
+        <v>20</v>
+      </c>
+      <c r="F160" s="142" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G160" s="142" t="s">
+        <v>56</v>
+      </c>
+      <c r="H160" s="142" t="s">
+        <v>22</v>
+      </c>
+      <c r="I160" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J160" s="142" t="s">
+        <v>978</v>
+      </c>
+      <c r="K160" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="L141" s="42">
-        <v>46139</v>
-      </c>
-      <c r="M141" s="53" t="s">
+      <c r="L160" s="143">
+        <v>46150</v>
+      </c>
+      <c r="M160" s="142" t="s">
+        <v>506</v>
+      </c>
+      <c r="N160" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="O160" s="142" t="s">
+        <v>33</v>
+      </c>
+      <c r="P160" s="142"/>
+      <c r="Q160" s="142" t="s">
+        <v>1017</v>
+      </c>
+      <c r="R160" s="142" t="s">
         <v>47</v>
       </c>
-      <c r="N141" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="O141" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="P141" s="53" t="s">
-        <v>621</v>
-      </c>
-      <c r="R141" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="S141" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="T141" s="53">
-        <v>904783.35999999999</v>
-      </c>
-      <c r="U141" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W141" s="53">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="142" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="138">
-        <v>45</v>
-      </c>
-      <c r="B142" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C142" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D142" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E142" s="53" t="s">
-        <v>779</v>
-      </c>
-      <c r="F142" s="53" t="s">
-        <v>951</v>
-      </c>
-      <c r="G142" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="H142" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="I142" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J142" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="K142" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="L142" s="42">
-        <v>46149</v>
-      </c>
-      <c r="M142" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="N142" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="O142" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q142" s="53" t="s">
-        <v>952</v>
-      </c>
-      <c r="R142" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="S142" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="T142" s="53">
-        <v>213955</v>
-      </c>
-      <c r="U142" s="53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="143" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="138">
-        <v>46</v>
-      </c>
-      <c r="B143" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C143" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D143" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="E143" s="53" t="s">
-        <v>592</v>
-      </c>
-      <c r="F143" s="53" t="s">
-        <v>953</v>
-      </c>
-      <c r="G143" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="H143" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="I143" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J143" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="K143" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L143" s="42">
-        <v>46153</v>
-      </c>
-      <c r="M143" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="N143" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="O143" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="P143" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q143" s="53" t="s">
-        <v>954</v>
-      </c>
-      <c r="R143" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="S143" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="T143" s="53">
-        <v>47777.97</v>
-      </c>
-      <c r="U143" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W143" s="53">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="144" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="138">
-        <v>47</v>
-      </c>
-      <c r="B144" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C144" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D144" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E144" s="53" t="s">
-        <v>955</v>
-      </c>
-      <c r="F144" s="53" t="s">
-        <v>956</v>
-      </c>
-      <c r="G144" s="53" t="s">
-        <v>79</v>
-      </c>
-      <c r="H144" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="I144" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J144" s="53" t="s">
-        <v>116</v>
-      </c>
-      <c r="K144" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L144" s="42">
-        <v>46154</v>
-      </c>
-      <c r="M144" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="N144" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="P144" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q144" s="53" t="s">
-        <v>117</v>
-      </c>
-      <c r="R144" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="S144" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="T144" s="53">
-        <v>18445</v>
-      </c>
-      <c r="U144" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W144" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="145" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="138">
-        <v>48</v>
-      </c>
-      <c r="B145" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C145" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D145" s="53" t="s">
-        <v>63</v>
-      </c>
-      <c r="E145" s="53" t="s">
-        <v>957</v>
-      </c>
-      <c r="F145" s="53" t="s">
-        <v>958</v>
-      </c>
-      <c r="G145" s="53" t="s">
-        <v>34</v>
-      </c>
-      <c r="H145" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="I145" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J145" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="K145" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="M145" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="O145" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="R145" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="S145" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="U145" s="53" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="146" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="138">
-        <v>49</v>
-      </c>
-      <c r="B146" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C146" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D146" s="53" t="s">
-        <v>959</v>
-      </c>
-      <c r="E146" s="53" t="s">
-        <v>960</v>
-      </c>
-      <c r="F146" s="53" t="s">
-        <v>961</v>
-      </c>
-      <c r="H146" s="53" t="s">
-        <v>80</v>
-      </c>
-      <c r="I146" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J146" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="K146" s="53" t="s">
-        <v>85</v>
-      </c>
-      <c r="L146" s="42">
-        <v>46162</v>
-      </c>
-      <c r="M146" s="53" t="s">
-        <v>962</v>
-      </c>
-      <c r="Q146" s="53" t="s">
-        <v>899</v>
-      </c>
-      <c r="R146" s="53" t="s">
-        <v>523</v>
-      </c>
-      <c r="S146" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="U146" s="53" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="147" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="138">
-        <v>50</v>
-      </c>
-      <c r="B147" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C147" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D147" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E147" s="53" t="s">
-        <v>546</v>
-      </c>
-      <c r="F147" s="53" t="s">
-        <v>963</v>
-      </c>
-      <c r="G147" s="53" t="s">
-        <v>508</v>
-      </c>
-      <c r="H147" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="I147" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J147" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="K147" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L147" s="42">
-        <v>46165</v>
-      </c>
-      <c r="M147" s="53" t="s">
-        <v>962</v>
-      </c>
-      <c r="N147" s="53" t="s">
-        <v>523</v>
-      </c>
-      <c r="O147" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="Q147" s="53" t="s">
-        <v>899</v>
-      </c>
-      <c r="R147" s="53" t="s">
-        <v>523</v>
-      </c>
-      <c r="S147" s="53" t="s">
-        <v>78</v>
-      </c>
-      <c r="T147" s="53">
-        <v>60000</v>
-      </c>
-      <c r="U147" s="53" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="148" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="138">
-        <v>51</v>
-      </c>
-      <c r="B148" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C148" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D148" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E148" s="53" t="s">
-        <v>779</v>
-      </c>
-      <c r="F148" s="53" t="s">
-        <v>964</v>
-      </c>
-      <c r="G148" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="H148" s="53" t="s">
-        <v>40</v>
-      </c>
-      <c r="I148" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J148" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="K148" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L148" s="42">
-        <v>46167</v>
-      </c>
-      <c r="M148" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="N148" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="O148" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="P148" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q148" s="53" t="s">
-        <v>965</v>
-      </c>
-      <c r="R148" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="S148" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="T148" s="53">
-        <v>137528</v>
-      </c>
-      <c r="U148" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W148" s="53">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="149" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="138">
-        <v>52</v>
-      </c>
-      <c r="B149" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C149" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D149" s="53" t="s">
-        <v>19</v>
-      </c>
-      <c r="E149" s="53" t="s">
-        <v>42</v>
-      </c>
-      <c r="F149" s="53" t="s">
-        <v>966</v>
-      </c>
-      <c r="H149" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="I149" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J149" s="53" t="s">
-        <v>88</v>
-      </c>
-      <c r="K149" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="L149" s="42">
-        <v>46156</v>
-      </c>
-      <c r="M149" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="N149" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="O149" s="53" t="s">
-        <v>90</v>
-      </c>
-      <c r="P149" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q149" s="53" t="s">
-        <v>967</v>
-      </c>
-      <c r="R149" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="S149" s="53" t="s">
-        <v>113</v>
-      </c>
-      <c r="T149" s="53">
-        <v>87726.85</v>
-      </c>
-      <c r="U149" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W149" s="53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="150" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="138">
-        <v>53</v>
-      </c>
-      <c r="B150" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C150" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D150" s="53" t="s">
-        <v>517</v>
-      </c>
-      <c r="E150" s="53" t="s">
-        <v>853</v>
-      </c>
-      <c r="F150" s="53" t="s">
-        <v>968</v>
-      </c>
-      <c r="G150" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="H150" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I150" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J150" s="53" t="s">
-        <v>881</v>
-      </c>
-      <c r="K150" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L150" s="42">
-        <v>46163</v>
-      </c>
-      <c r="M150" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="N150" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="O150" s="53" t="s">
-        <v>969</v>
-      </c>
-      <c r="R150" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="S150" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="T150" s="53">
-        <v>61684</v>
-      </c>
-      <c r="U150" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W150" s="53">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="151" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="138">
-        <v>54</v>
-      </c>
-      <c r="B151" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C151" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D151" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E151" s="53" t="s">
-        <v>970</v>
-      </c>
-      <c r="F151" s="53" t="s">
-        <v>971</v>
-      </c>
-      <c r="G151" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="H151" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="I151" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J151" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="K151" s="53" t="s">
-        <v>58</v>
-      </c>
-      <c r="L151" s="42">
-        <v>46160</v>
-      </c>
-      <c r="M151" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="N151" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="O151" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="P151" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q151" s="53" t="s">
-        <v>972</v>
-      </c>
-      <c r="R151" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="S151" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="T151" s="53">
-        <v>78815</v>
-      </c>
-      <c r="U151" s="53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="152" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="138">
-        <v>55</v>
-      </c>
-      <c r="B152" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C152" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D152" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E152" s="53" t="s">
-        <v>64</v>
-      </c>
-      <c r="F152" s="53" t="s">
-        <v>973</v>
-      </c>
-      <c r="G152" s="53" t="s">
-        <v>50</v>
-      </c>
-      <c r="H152" s="53" t="s">
-        <v>51</v>
-      </c>
-      <c r="I152" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J152" s="53" t="s">
-        <v>974</v>
-      </c>
-      <c r="K152" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L152" s="42">
-        <v>46167</v>
-      </c>
-      <c r="M152" s="53" t="s">
-        <v>53</v>
-      </c>
-      <c r="N152" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="O152" s="53" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q152" s="53" t="s">
-        <v>975</v>
-      </c>
-      <c r="R152" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="S152" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="T152" s="53">
-        <v>122050.6</v>
-      </c>
-      <c r="U152" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W152" s="53">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="153" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="138">
-        <v>56</v>
-      </c>
-      <c r="B153" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C153" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D153" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E153" s="53" t="s">
-        <v>562</v>
-      </c>
-      <c r="F153" s="53" t="s">
-        <v>976</v>
-      </c>
-      <c r="G153" s="53" t="s">
-        <v>977</v>
-      </c>
-      <c r="H153" s="53" t="s">
-        <v>713</v>
-      </c>
-      <c r="I153" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="J153" s="53" t="s">
-        <v>978</v>
-      </c>
-      <c r="K153" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L153" s="42">
-        <v>46176</v>
-      </c>
-      <c r="M153" s="53" t="s">
-        <v>506</v>
-      </c>
-      <c r="N153" s="53" t="s">
-        <v>621</v>
-      </c>
-      <c r="O153" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="P153" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q153" s="53" t="s">
-        <v>979</v>
-      </c>
-      <c r="R153" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="S153" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="T153" s="53">
-        <v>60166.16</v>
-      </c>
-      <c r="U153" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W153" s="53">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="154" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="138">
-        <v>54</v>
-      </c>
-      <c r="B154" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C154" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D154" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="E154" s="53" t="s">
-        <v>980</v>
-      </c>
-      <c r="F154" s="53" t="s">
-        <v>981</v>
-      </c>
-      <c r="G154" s="53" t="s">
-        <v>39</v>
-      </c>
-      <c r="H154" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="I154" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J154" s="53" t="s">
-        <v>978</v>
-      </c>
-      <c r="K154" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L154" s="42">
-        <v>46169</v>
-      </c>
-      <c r="M154" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="N154" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="O154" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="R154" s="53" t="s">
-        <v>109</v>
-      </c>
-      <c r="S154" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="T154" s="53">
-        <v>33017.660000000003</v>
-      </c>
-      <c r="U154" s="53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="155" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="138">
-        <v>55</v>
-      </c>
-      <c r="B155" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C155" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D155" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E155" s="53" t="s">
-        <v>562</v>
-      </c>
-      <c r="F155" s="53" t="s">
-        <v>982</v>
-      </c>
-      <c r="G155" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="H155" s="53" t="s">
-        <v>526</v>
-      </c>
-      <c r="I155" s="53" t="s">
-        <v>62</v>
-      </c>
-      <c r="J155" s="53" t="s">
-        <v>983</v>
-      </c>
-      <c r="K155" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L155" s="42">
-        <v>46185</v>
-      </c>
-      <c r="M155" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="N155" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="O155" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="P155" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="R155" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="S155" s="53" t="s">
-        <v>54</v>
-      </c>
-      <c r="U155" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="W155" s="53">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="156" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="138">
-        <v>56</v>
-      </c>
-      <c r="B156" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C156" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D156" s="53" t="s">
-        <v>83</v>
-      </c>
-      <c r="E156" s="53" t="s">
-        <v>984</v>
-      </c>
-      <c r="F156" s="53" t="s">
-        <v>985</v>
-      </c>
-      <c r="K156" s="53" t="s">
-        <v>77</v>
-      </c>
-      <c r="L156" s="42">
-        <v>46171</v>
-      </c>
-      <c r="M156" s="53" t="s">
-        <v>506</v>
-      </c>
-      <c r="N156" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="O156" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="P156" s="53" t="s">
-        <v>92</v>
-      </c>
-      <c r="R156" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="S156" s="53" t="s">
-        <v>43</v>
-      </c>
-      <c r="T156" s="53">
-        <v>77099.490000000005</v>
-      </c>
-      <c r="U156" s="53" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="157" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="138">
-        <v>57</v>
-      </c>
-      <c r="B157" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C157" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D157" s="53" t="s">
-        <v>799</v>
-      </c>
-      <c r="E157" s="53" t="s">
-        <v>509</v>
-      </c>
-      <c r="F157" s="53" t="s">
-        <v>986</v>
-      </c>
-      <c r="L157" s="42">
-        <v>46181</v>
-      </c>
-      <c r="M157" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="N157" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="O157" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="P157" s="53" t="s">
-        <v>621</v>
-      </c>
-      <c r="R157" s="53" t="s">
-        <v>538</v>
-      </c>
-      <c r="S157" s="53" t="s">
-        <v>52</v>
-      </c>
-      <c r="T157" s="53">
-        <v>15000</v>
-      </c>
-      <c r="U157" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W157" s="53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="158" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="138">
-        <v>58</v>
-      </c>
-      <c r="B158" s="51">
-        <v>2026</v>
-      </c>
-      <c r="C158" s="117" t="s">
-        <v>87</v>
-      </c>
-      <c r="D158" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="E158" s="53" t="s">
-        <v>987</v>
-      </c>
-      <c r="F158" s="53" t="s">
-        <v>988</v>
-      </c>
-      <c r="G158" s="53" t="s">
-        <v>508</v>
-      </c>
-      <c r="H158" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I158" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="J158" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="K158" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L158" s="42">
-        <v>46178</v>
-      </c>
-      <c r="M158" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="N158" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="O158" s="53" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q158" s="53" t="s">
-        <v>989</v>
-      </c>
-      <c r="R158" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="S158" s="53" t="s">
-        <v>41</v>
-      </c>
-      <c r="T158" s="53">
-        <v>167739.19</v>
-      </c>
-      <c r="U158" s="53" t="s">
-        <v>49</v>
-      </c>
-      <c r="W158" s="53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="159" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="138">
-        <v>59</v>
-      </c>
-      <c r="B159" s="126">
-        <v>2026</v>
-      </c>
-      <c r="C159" s="128" t="s">
-        <v>87</v>
-      </c>
-      <c r="D159" s="53" t="s">
-        <v>30</v>
-      </c>
-      <c r="E159" s="53" t="s">
-        <v>990</v>
-      </c>
-      <c r="F159" s="57" t="s">
-        <v>991</v>
-      </c>
-      <c r="G159" s="53" t="s">
-        <v>74</v>
-      </c>
-      <c r="H159" s="53" t="s">
-        <v>44</v>
-      </c>
-      <c r="I159" s="53" t="s">
-        <v>104</v>
-      </c>
-      <c r="J159" s="53" t="s">
-        <v>24</v>
-      </c>
-      <c r="K159" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L159" s="141">
-        <v>46195</v>
-      </c>
-      <c r="M159" s="67" t="s">
-        <v>60</v>
-      </c>
-      <c r="N159" s="53" t="s">
-        <v>32</v>
-      </c>
-      <c r="O159" s="53" t="s">
-        <v>89</v>
-      </c>
-      <c r="R159" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="S159" s="53" t="s">
-        <v>28</v>
-      </c>
-      <c r="U159" s="53" t="s">
-        <v>95</v>
-      </c>
-      <c r="W159" s="53">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="160" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="138">
-        <v>60</v>
-      </c>
-      <c r="B160" s="126">
-        <v>2026</v>
-      </c>
-      <c r="C160" s="128" t="s">
-        <v>87</v>
-      </c>
-      <c r="D160" s="53" t="s">
-        <v>55</v>
-      </c>
-      <c r="E160" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="F160" s="57" t="s">
-        <v>992</v>
-      </c>
-      <c r="G160" s="53" t="s">
-        <v>56</v>
-      </c>
-      <c r="H160" s="53" t="s">
-        <v>22</v>
-      </c>
-      <c r="I160" s="53" t="s">
-        <v>23</v>
-      </c>
-      <c r="J160" s="53" t="s">
-        <v>978</v>
-      </c>
-      <c r="K160" s="53" t="s">
-        <v>25</v>
-      </c>
-      <c r="L160" s="141">
-        <v>46150</v>
-      </c>
-      <c r="M160" s="67" t="s">
-        <v>506</v>
-      </c>
-      <c r="N160" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="O160" s="53" t="s">
-        <v>33</v>
-      </c>
-      <c r="Q160" s="53" t="s">
-        <v>993</v>
-      </c>
-      <c r="R160" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="S160" s="53" t="s">
+      <c r="S160" s="142" t="s">
         <v>90</v>
       </c>
       <c r="T160" s="142">
         <v>300474.76</v>
       </c>
-      <c r="U160" s="53" t="s">
+      <c r="U160" s="142" t="s">
         <v>70</v>
       </c>
-      <c r="W160" s="53">
+      <c r="V160" s="142"/>
+      <c r="W160" s="142">
         <v>4</v>
       </c>
     </row>
     <row r="161" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="138">
-        <v>61</v>
-      </c>
-      <c r="B161" s="126">
+      <c r="A161" s="121">
+        <v>65</v>
+      </c>
+      <c r="B161" s="140">
         <v>2026</v>
       </c>
-      <c r="C161" s="128" t="s">
+      <c r="C161" s="141" t="s">
         <v>87</v>
       </c>
-      <c r="D161" s="53" t="s">
+      <c r="D161" s="142" t="s">
         <v>83</v>
       </c>
-      <c r="E161" s="53" t="s">
-        <v>994</v>
-      </c>
-      <c r="F161" s="57" t="s">
-        <v>995</v>
-      </c>
-      <c r="G161" s="53" t="s">
+      <c r="E161" s="142" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F161" s="142" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G161" s="142" t="s">
         <v>39</v>
       </c>
-      <c r="H161" s="53" t="s">
+      <c r="H161" s="142" t="s">
         <v>44</v>
       </c>
-      <c r="I161" s="53" t="s">
+      <c r="I161" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="J161" s="53" t="s">
+      <c r="J161" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="K161" s="53" t="s">
+      <c r="K161" s="142" t="s">
         <v>58</v>
       </c>
-      <c r="L161" s="141">
+      <c r="L161" s="143">
         <v>46181</v>
       </c>
-      <c r="M161" s="67" t="s">
+      <c r="M161" s="142" t="s">
         <v>46</v>
       </c>
-      <c r="N161" s="53" t="s">
+      <c r="N161" s="142" t="s">
         <v>48</v>
       </c>
-      <c r="O161" s="53" t="s">
+      <c r="O161" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="R161" s="53" t="s">
+      <c r="P161" s="142"/>
+      <c r="Q161" s="142"/>
+      <c r="R161" s="142" t="s">
         <v>59</v>
       </c>
-      <c r="S161" s="53" t="s">
+      <c r="S161" s="142" t="s">
         <v>54</v>
       </c>
       <c r="T161" s="142">
         <v>80568.2</v>
       </c>
-      <c r="U161" s="53" t="s">
+      <c r="U161" s="142" t="s">
         <v>946</v>
       </c>
-      <c r="W161" s="53">
+      <c r="V161" s="142"/>
+      <c r="W161" s="142">
         <v>4</v>
       </c>
     </row>
     <row r="162" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="5"/>
+      <c r="A162" s="121">
+        <v>66</v>
+      </c>
+      <c r="B162" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C162" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D162" s="142" t="s">
+        <v>83</v>
+      </c>
+      <c r="E162" s="142" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F162" s="142" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G162" s="142" t="s">
+        <v>612</v>
+      </c>
+      <c r="H162" s="142" t="s">
+        <v>22</v>
+      </c>
+      <c r="I162" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J162" s="142" t="s">
+        <v>1022</v>
+      </c>
+      <c r="K162" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L162" s="143">
+        <v>46209</v>
+      </c>
+      <c r="M162" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="N162" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="O162" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="P162" s="142"/>
+      <c r="Q162" s="142"/>
+      <c r="R162" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="S162" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="T162" s="142">
+        <v>22500</v>
+      </c>
+      <c r="U162" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V162" s="37">
+        <v>46209</v>
+      </c>
+      <c r="W162" s="142">
+        <v>4</v>
+      </c>
     </row>
     <row r="163" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="5"/>
+      <c r="A163" s="121">
+        <v>67</v>
+      </c>
+      <c r="B163" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C163" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D163" s="142" t="s">
+        <v>19</v>
+      </c>
+      <c r="E163" s="142" t="s">
+        <v>20</v>
+      </c>
+      <c r="F163" s="142" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G163" s="142" t="s">
+        <v>612</v>
+      </c>
+      <c r="H163" s="142" t="s">
+        <v>80</v>
+      </c>
+      <c r="I163" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J163" s="142" t="s">
+        <v>106</v>
+      </c>
+      <c r="K163" s="142" t="s">
+        <v>1024</v>
+      </c>
+      <c r="L163" s="143">
+        <v>46210</v>
+      </c>
+      <c r="M163" s="142"/>
+      <c r="N163" s="142" t="s">
+        <v>36</v>
+      </c>
+      <c r="O163" s="142" t="s">
+        <v>89</v>
+      </c>
+      <c r="P163" s="142" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q163" s="142"/>
+      <c r="R163" s="142"/>
+      <c r="S163" s="142" t="s">
+        <v>78</v>
+      </c>
+      <c r="T163" s="142">
+        <v>100000</v>
+      </c>
+      <c r="U163" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V163" s="142"/>
+      <c r="W163" s="142">
+        <v>6</v>
+      </c>
     </row>
     <row r="164" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="5"/>
+      <c r="A164" s="121">
+        <v>68</v>
+      </c>
+      <c r="B164" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C164" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D164" s="142" t="s">
+        <v>83</v>
+      </c>
+      <c r="E164" s="142" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F164" s="142" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G164" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H164" s="142" t="s">
+        <v>80</v>
+      </c>
+      <c r="I164" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J164" s="142" t="s">
+        <v>978</v>
+      </c>
+      <c r="K164" s="142" t="s">
+        <v>25</v>
+      </c>
+      <c r="L164" s="143">
+        <v>46183</v>
+      </c>
+      <c r="M164" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="N164" s="142"/>
+      <c r="O164" s="142"/>
+      <c r="P164" s="142"/>
+      <c r="Q164" s="142" t="s">
+        <v>1027</v>
+      </c>
+      <c r="R164" s="142" t="s">
+        <v>53</v>
+      </c>
+      <c r="S164" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T164" s="142">
+        <v>112607</v>
+      </c>
+      <c r="U164" s="142" t="s">
+        <v>70</v>
+      </c>
+      <c r="V164" s="142"/>
+      <c r="W164" s="142"/>
     </row>
     <row r="165" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="5"/>
+      <c r="A165" s="121">
+        <v>69</v>
+      </c>
+      <c r="B165" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C165" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D165" s="142" t="s">
+        <v>30</v>
+      </c>
+      <c r="E165" s="142" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F165" s="142" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G165" s="142" t="s">
+        <v>640</v>
+      </c>
+      <c r="H165" s="142" t="s">
+        <v>40</v>
+      </c>
+      <c r="I165" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J165" s="142" t="s">
+        <v>605</v>
+      </c>
+      <c r="K165" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="L165" s="143">
+        <v>46211</v>
+      </c>
+      <c r="M165" s="142" t="s">
+        <v>67</v>
+      </c>
+      <c r="N165" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="O165" s="142" t="s">
+        <v>27</v>
+      </c>
+      <c r="P165" s="142"/>
+      <c r="Q165" s="142"/>
+      <c r="R165" s="142" t="s">
+        <v>67</v>
+      </c>
+      <c r="S165" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="T165" s="142"/>
+      <c r="U165" s="142" t="s">
+        <v>95</v>
+      </c>
+      <c r="V165" s="142"/>
+      <c r="W165" s="142"/>
     </row>
     <row r="166" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="5"/>
+      <c r="A166" s="142">
+        <v>70</v>
+      </c>
+      <c r="B166" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C166" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D166" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E166" s="142" t="s">
+        <v>543</v>
+      </c>
+      <c r="F166" s="142" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G166" s="142" t="s">
+        <v>56</v>
+      </c>
+      <c r="H166" s="142" t="s">
+        <v>80</v>
+      </c>
+      <c r="I166" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J166" s="142" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K166" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="L166" s="143">
+        <v>46203</v>
+      </c>
+      <c r="M166" s="142"/>
+      <c r="N166" s="142" t="s">
+        <v>48</v>
+      </c>
+      <c r="O166" s="142" t="s">
+        <v>53</v>
+      </c>
+      <c r="P166" s="142"/>
+      <c r="Q166" s="142"/>
+      <c r="R166" s="142" t="s">
+        <v>65</v>
+      </c>
+      <c r="S166" s="142" t="s">
+        <v>82</v>
+      </c>
+      <c r="T166" s="142">
+        <v>76394.41</v>
+      </c>
+      <c r="U166" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V166" s="142"/>
+      <c r="W166" s="142">
+        <v>5</v>
+      </c>
     </row>
     <row r="167" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="5"/>
+      <c r="A167" s="142">
+        <v>71</v>
+      </c>
+      <c r="B167" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C167" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D167" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E167" s="142" t="s">
+        <v>99</v>
+      </c>
+      <c r="F167" s="142" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G167" s="142" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H167" s="142" t="s">
+        <v>51</v>
+      </c>
+      <c r="I167" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J167" s="142" t="s">
+        <v>68</v>
+      </c>
+      <c r="K167" s="142" t="s">
+        <v>77</v>
+      </c>
+      <c r="L167" s="143">
+        <v>46203</v>
+      </c>
+      <c r="M167" s="142" t="s">
+        <v>621</v>
+      </c>
+      <c r="N167" s="142" t="s">
+        <v>46</v>
+      </c>
+      <c r="O167" s="142" t="s">
+        <v>47</v>
+      </c>
+      <c r="P167" s="142"/>
+      <c r="Q167" s="142" t="s">
+        <v>1034</v>
+      </c>
+      <c r="R167" s="142" t="s">
+        <v>61</v>
+      </c>
+      <c r="S167" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="T167" s="142">
+        <v>27607</v>
+      </c>
+      <c r="U167" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V167" s="142"/>
+      <c r="W167" s="142">
+        <v>3</v>
+      </c>
     </row>
     <row r="168" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="5"/>
+      <c r="A168" s="142">
+        <v>72</v>
+      </c>
+      <c r="B168" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C168" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D168" s="142" t="s">
+        <v>83</v>
+      </c>
+      <c r="E168" s="142" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F168" s="142" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G168" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H168" s="142" t="s">
+        <v>80</v>
+      </c>
+      <c r="I168" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J168" s="142" t="s">
+        <v>24</v>
+      </c>
+      <c r="K168" s="142" t="s">
+        <v>85</v>
+      </c>
+      <c r="L168" s="143">
+        <v>46206</v>
+      </c>
+      <c r="M168" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="N168" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="O168" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="P168" s="142"/>
+      <c r="Q168" s="142"/>
+      <c r="R168" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="S168" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T168" s="142">
+        <v>35550</v>
+      </c>
+      <c r="U168" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V168" s="142"/>
+      <c r="W168" s="142"/>
     </row>
     <row r="169" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="5"/>
+      <c r="A169" s="142">
+        <v>73</v>
+      </c>
+      <c r="B169" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C169" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D169" s="142" t="s">
+        <v>83</v>
+      </c>
+      <c r="E169" s="142" t="s">
+        <v>1037</v>
+      </c>
+      <c r="F169" s="142" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G169" s="142" t="s">
+        <v>640</v>
+      </c>
+      <c r="H169" s="142" t="s">
+        <v>22</v>
+      </c>
+      <c r="I169" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J169" s="142" t="s">
+        <v>24</v>
+      </c>
+      <c r="K169" s="142" t="s">
+        <v>85</v>
+      </c>
+      <c r="L169" s="143">
+        <v>46209</v>
+      </c>
+      <c r="M169" s="142"/>
+      <c r="N169" s="142" t="s">
+        <v>65</v>
+      </c>
+      <c r="O169" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="P169" s="142"/>
+      <c r="Q169" s="142"/>
+      <c r="R169" s="142"/>
+      <c r="S169" s="142" t="s">
+        <v>28</v>
+      </c>
+      <c r="T169" s="142"/>
+      <c r="U169" s="142"/>
+      <c r="V169" s="142"/>
+      <c r="W169" s="142"/>
     </row>
     <row r="170" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="5"/>
+      <c r="A170" s="142">
+        <v>74</v>
+      </c>
+      <c r="B170" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C170" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D170" s="142" t="s">
+        <v>30</v>
+      </c>
+      <c r="E170" s="142" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F170" s="142" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G170" s="142" t="s">
+        <v>1033</v>
+      </c>
+      <c r="H170" s="142" t="s">
+        <v>567</v>
+      </c>
+      <c r="I170" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J170" s="142" t="s">
+        <v>71</v>
+      </c>
+      <c r="K170" s="142" t="s">
+        <v>85</v>
+      </c>
+      <c r="L170" s="143">
+        <v>46185</v>
+      </c>
+      <c r="M170" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="N170" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="O170" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="P170" s="142"/>
+      <c r="Q170" s="142" t="s">
+        <v>952</v>
+      </c>
+      <c r="R170" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="S170" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="T170" s="142">
+        <v>24000</v>
+      </c>
+      <c r="U170" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V170" s="142"/>
+      <c r="W170" s="142"/>
     </row>
     <row r="171" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="5"/>
+      <c r="A171" s="142">
+        <v>75</v>
+      </c>
+      <c r="B171" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C171" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D171" s="142" t="s">
+        <v>19</v>
+      </c>
+      <c r="E171" s="142" t="s">
+        <v>606</v>
+      </c>
+      <c r="F171" s="142" t="s">
+        <v>1041</v>
+      </c>
+      <c r="G171" s="142" t="s">
+        <v>50</v>
+      </c>
+      <c r="H171" s="142" t="s">
+        <v>40</v>
+      </c>
+      <c r="I171" s="142" t="s">
+        <v>62</v>
+      </c>
+      <c r="J171" s="142" t="s">
+        <v>533</v>
+      </c>
+      <c r="K171" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="L171" s="143">
+        <v>46202</v>
+      </c>
+      <c r="M171" s="142" t="s">
+        <v>506</v>
+      </c>
+      <c r="N171" s="142" t="s">
+        <v>46</v>
+      </c>
+      <c r="O171" s="142" t="s">
+        <v>65</v>
+      </c>
+      <c r="P171" s="142"/>
+      <c r="Q171" s="142" t="s">
+        <v>975</v>
+      </c>
+      <c r="R171" s="142" t="s">
+        <v>506</v>
+      </c>
+      <c r="S171" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="T171" s="142"/>
+      <c r="U171" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V171" s="142"/>
+      <c r="W171" s="142">
+        <v>36</v>
+      </c>
     </row>
     <row r="172" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="5"/>
+      <c r="A172" s="142">
+        <v>76</v>
+      </c>
+      <c r="B172" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C172" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D172" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E172" s="142" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F172" s="142"/>
+      <c r="G172" s="142"/>
+      <c r="H172" s="142"/>
+      <c r="I172" s="142"/>
+      <c r="J172" s="142"/>
+      <c r="K172" s="142" t="s">
+        <v>77</v>
+      </c>
+      <c r="L172" s="143"/>
+      <c r="M172" s="142"/>
+      <c r="N172" s="142"/>
+      <c r="O172" s="142"/>
+      <c r="P172" s="142"/>
+      <c r="Q172" s="142"/>
+      <c r="R172" s="142" t="s">
+        <v>61</v>
+      </c>
+      <c r="S172" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="T172" s="142"/>
+      <c r="U172" s="142" t="s">
+        <v>38</v>
+      </c>
+      <c r="V172" s="142"/>
+      <c r="W172" s="142"/>
     </row>
     <row r="173" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="5"/>
+      <c r="A173" s="142">
+        <v>77</v>
+      </c>
+      <c r="B173" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C173" s="141" t="s">
+        <v>87</v>
+      </c>
+      <c r="D173" s="142" t="s">
+        <v>30</v>
+      </c>
+      <c r="E173" s="142" t="s">
+        <v>565</v>
+      </c>
+      <c r="F173" s="142"/>
+      <c r="G173" s="142"/>
+      <c r="H173" s="142"/>
+      <c r="I173" s="142"/>
+      <c r="J173" s="142"/>
+      <c r="K173" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="L173" s="143"/>
+      <c r="M173" s="142"/>
+      <c r="N173" s="142" t="s">
+        <v>538</v>
+      </c>
+      <c r="O173" s="142" t="s">
+        <v>538</v>
+      </c>
+      <c r="P173" s="142"/>
+      <c r="Q173" s="142"/>
+      <c r="R173" s="142" t="s">
+        <v>538</v>
+      </c>
+      <c r="S173" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="T173" s="142"/>
+      <c r="U173" s="142" t="s">
+        <v>95</v>
+      </c>
+      <c r="V173" s="142"/>
+      <c r="W173" s="142"/>
     </row>
     <row r="174" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="5"/>
+      <c r="A174" s="142">
+        <v>78</v>
+      </c>
+      <c r="B174" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C174" s="141" t="s">
+        <v>681</v>
+      </c>
+      <c r="D174" s="142" t="s">
+        <v>55</v>
+      </c>
+      <c r="E174" s="142" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F174" s="142" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G174" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H174" s="142" t="s">
+        <v>40</v>
+      </c>
+      <c r="I174" s="142" t="s">
+        <v>23</v>
+      </c>
+      <c r="J174" s="142" t="s">
+        <v>881</v>
+      </c>
+      <c r="K174" s="142" t="s">
+        <v>58</v>
+      </c>
+      <c r="L174" s="143">
+        <v>46211</v>
+      </c>
+      <c r="M174" s="142" t="s">
+        <v>67</v>
+      </c>
+      <c r="N174" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="O174" s="142" t="s">
+        <v>538</v>
+      </c>
+      <c r="P174" s="142"/>
+      <c r="Q174" s="142" t="s">
+        <v>1045</v>
+      </c>
+      <c r="R174" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="S174" s="142" t="s">
+        <v>54</v>
+      </c>
+      <c r="T174" s="142">
+        <v>98440.5</v>
+      </c>
+      <c r="U174" s="142" t="s">
+        <v>49</v>
+      </c>
+      <c r="V174" s="142"/>
+      <c r="W174" s="142">
+        <v>12</v>
+      </c>
     </row>
     <row r="175" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="5"/>
+      <c r="A175" s="142">
+        <v>79</v>
+      </c>
+      <c r="B175" s="140">
+        <v>2026</v>
+      </c>
+      <c r="C175" s="141" t="s">
+        <v>681</v>
+      </c>
+      <c r="D175" s="142" t="s">
+        <v>83</v>
+      </c>
+      <c r="E175" s="142" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F175" s="142" t="s">
+        <v>1047</v>
+      </c>
+      <c r="G175" s="142" t="s">
+        <v>39</v>
+      </c>
+      <c r="H175" s="142"/>
+      <c r="I175" s="142"/>
+      <c r="J175" s="142"/>
+      <c r="K175" s="142" t="s">
+        <v>85</v>
+      </c>
+      <c r="L175" s="143"/>
+      <c r="M175" s="142" t="s">
+        <v>46</v>
+      </c>
+      <c r="N175" s="142" t="s">
+        <v>43</v>
+      </c>
+      <c r="O175" s="142" t="s">
+        <v>32</v>
+      </c>
+      <c r="P175" s="142"/>
+      <c r="Q175" s="142"/>
+      <c r="R175" s="142" t="s">
+        <v>538</v>
+      </c>
+      <c r="S175" s="142" t="s">
+        <v>41</v>
+      </c>
+      <c r="T175" s="142"/>
+      <c r="U175" s="142" t="s">
+        <v>95</v>
+      </c>
+      <c r="V175" s="142"/>
+      <c r="W175" s="142"/>
     </row>
     <row r="176" spans="1:23" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="5"/>
-    </row>
-    <row r="177" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="5"/>
-    </row>
-    <row r="178" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="5"/>
-    </row>
-    <row r="179" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="5"/>
-    </row>
-    <row r="180" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="5"/>
-    </row>
-    <row r="181" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="5"/>
-    </row>
-    <row r="182" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="5"/>
-    </row>
-    <row r="183" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="5"/>
-    </row>
-    <row r="184" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="5"/>
-    </row>
-    <row r="185" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="5"/>
-    </row>
-    <row r="186" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="5"/>
-    </row>
-    <row r="187" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="5"/>
-    </row>
-    <row r="188" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="5"/>
-    </row>
-    <row r="189" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="5"/>
-    </row>
-    <row r="190" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="5"/>
-    </row>
-    <row r="191" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="5"/>
-    </row>
-    <row r="192" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="5"/>
-    </row>
-    <row r="193" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="5"/>
-    </row>
-    <row r="194" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="5"/>
-    </row>
-    <row r="195" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="5"/>
-    </row>
-    <row r="196" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="5"/>
-    </row>
-    <row r="197" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="5"/>
-    </row>
-    <row r="198" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="5"/>
-    </row>
-    <row r="199" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="5"/>
-    </row>
-    <row r="200" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="5"/>
-    </row>
-    <row r="201" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="5"/>
-    </row>
-    <row r="202" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="5"/>
-    </row>
-    <row r="203" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="5"/>
-    </row>
-    <row r="204" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="5"/>
-    </row>
-    <row r="205" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="5"/>
-    </row>
-    <row r="206" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="5"/>
-    </row>
-    <row r="207" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="5"/>
-    </row>
-    <row r="208" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="5"/>
-    </row>
-    <row r="209" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="5"/>
-    </row>
-    <row r="210" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="5"/>
-    </row>
-    <row r="211" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="5"/>
-    </row>
-    <row r="212" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="5"/>
-    </row>
-    <row r="213" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="5"/>
-    </row>
-    <row r="214" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="5"/>
-    </row>
-    <row r="215" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="5"/>
-    </row>
-    <row r="216" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="5"/>
-    </row>
-    <row r="217" spans="1:1" ht="10" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="5"/>
+      <c r="A176" s="58"/>
+      <c r="B176" s="58"/>
+    </row>
+    <row r="177" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="58"/>
+      <c r="B177" s="58"/>
+    </row>
+    <row r="178" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A178" s="58"/>
+      <c r="B178" s="58"/>
+    </row>
+    <row r="179" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A179" s="58"/>
+      <c r="B179" s="58"/>
+    </row>
+    <row r="180" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="58"/>
+      <c r="B180" s="58"/>
+    </row>
+    <row r="181" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A181" s="58"/>
+      <c r="B181" s="58"/>
+    </row>
+    <row r="182" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A182" s="58"/>
+      <c r="B182" s="58"/>
+    </row>
+    <row r="183" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="58"/>
+      <c r="B183" s="58"/>
+    </row>
+    <row r="184" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A184" s="58"/>
+      <c r="B184" s="58"/>
+    </row>
+    <row r="185" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="58"/>
+      <c r="B185" s="58"/>
+    </row>
+    <row r="186" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="58"/>
+      <c r="B186" s="58"/>
+    </row>
+    <row r="187" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A187" s="58"/>
+      <c r="B187" s="58"/>
+    </row>
+    <row r="188" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A188" s="58"/>
+      <c r="B188" s="58"/>
+    </row>
+    <row r="189" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="58"/>
+      <c r="B189" s="58"/>
+    </row>
+    <row r="190" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A190" s="58"/>
+      <c r="B190" s="58"/>
+    </row>
+    <row r="191" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A191" s="58"/>
+      <c r="B191" s="58"/>
+    </row>
+    <row r="192" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="58"/>
+      <c r="B192" s="58"/>
+    </row>
+    <row r="193" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A193" s="58"/>
+      <c r="B193" s="58"/>
+    </row>
+    <row r="194" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A194" s="58"/>
+      <c r="B194" s="58"/>
+    </row>
+    <row r="195" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="58"/>
+      <c r="B195" s="58"/>
+    </row>
+    <row r="196" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A196" s="58"/>
+      <c r="B196" s="58"/>
+    </row>
+    <row r="197" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A197" s="58"/>
+      <c r="B197" s="58"/>
+    </row>
+    <row r="198" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A198" s="58"/>
+      <c r="B198" s="58"/>
+    </row>
+    <row r="199" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A199" s="58"/>
+      <c r="B199" s="58"/>
+    </row>
+    <row r="200" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A200" s="58"/>
+      <c r="B200" s="58"/>
+    </row>
+    <row r="201" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A201" s="58"/>
+      <c r="B201" s="58"/>
+    </row>
+    <row r="202" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" s="58"/>
+      <c r="B202" s="58"/>
+    </row>
+    <row r="203" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" s="58"/>
+      <c r="B203" s="58"/>
+    </row>
+    <row r="204" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A204" s="58"/>
+      <c r="B204" s="58"/>
+    </row>
+    <row r="205" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A205" s="58"/>
+      <c r="B205" s="58"/>
+    </row>
+    <row r="206" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" s="58"/>
+      <c r="B206" s="58"/>
+    </row>
+    <row r="207" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" s="58"/>
+      <c r="B207" s="58"/>
+    </row>
+    <row r="208" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" s="58"/>
+      <c r="B208" s="58"/>
+    </row>
+    <row r="209" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A209" s="58"/>
+      <c r="B209" s="58"/>
+    </row>
+    <row r="210" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A210" s="58"/>
+      <c r="B210" s="58"/>
+    </row>
+    <row r="211" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A211" s="58"/>
+      <c r="B211" s="58"/>
+    </row>
+    <row r="212" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A212" s="58"/>
+      <c r="B212" s="58"/>
+    </row>
+    <row r="213" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A213" s="58"/>
+      <c r="B213" s="58"/>
+    </row>
+    <row r="214" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="58"/>
+      <c r="B214" s="58"/>
+    </row>
+    <row r="215" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="58"/>
+      <c r="B215" s="58"/>
+    </row>
+    <row r="216" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="58"/>
+      <c r="B216" s="58"/>
+    </row>
+    <row r="217" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" s="58"/>
+      <c r="B217" s="58"/>
+    </row>
+    <row r="218" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" s="58"/>
+      <c r="B218" s="58"/>
+    </row>
+    <row r="219" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" s="58"/>
+      <c r="B219" s="58"/>
+    </row>
+    <row r="220" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="58"/>
+      <c r="B220" s="58"/>
+    </row>
+    <row r="221" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" s="58"/>
+      <c r="B221" s="58"/>
+    </row>
+    <row r="222" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" s="58"/>
+      <c r="B222" s="58"/>
+    </row>
+    <row r="223" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" s="58"/>
+      <c r="B223" s="58"/>
+    </row>
+    <row r="224" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" s="58"/>
+      <c r="B224" s="58"/>
+    </row>
+    <row r="225" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" s="58"/>
+      <c r="B225" s="58"/>
+    </row>
+    <row r="226" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" s="58"/>
+      <c r="B226" s="58"/>
+    </row>
+    <row r="227" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="58"/>
+      <c r="B227" s="58"/>
+    </row>
+    <row r="228" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" s="58"/>
+      <c r="B228" s="58"/>
+    </row>
+    <row r="229" spans="1:2" ht="10" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" s="58"/>
+      <c r="B229" s="58"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:W139" xr:uid="{7F7F4377-AB0D-4AD1-9A42-D0995505B602}">
@@ -19825,11 +21239,11 @@
   </autoFilter>
   <phoneticPr fontId="42" type="noConversion"/>
   <dataValidations count="9">
-    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V97:V139 L97:L158 L162:L1048576 U159:U161 M159:M161" xr:uid="{7C384ADE-763A-4BD1-83BF-4E824E178031}">
+    <dataValidation type="date" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="V97:V139 L97:L1048576 V159:V175" xr:uid="{7C384ADE-763A-4BD1-83BF-4E824E178031}">
       <formula1>46023</formula1>
       <formula2>46387</formula2>
     </dataValidation>
-    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="Its should be between $10,000 &amp; $2,000,000" sqref="T97:T128 T130:T139" xr:uid="{51954289-ACB0-454F-99F1-DE0415916F7B}">
+    <dataValidation type="decimal" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="Its should be between $10,000 &amp; $2,000,000" sqref="T97:T128 T130:T139 T159:T161" xr:uid="{51954289-ACB0-454F-99F1-DE0415916F7B}">
       <formula1>10000</formula1>
       <formula2>3000000</formula2>
     </dataValidation>
@@ -19837,15 +21251,15 @@
       <formula1>46023</formula1>
       <formula2>46034</formula2>
     </dataValidation>
-    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="It should be in months" sqref="W97:W139 V2:V42 V47:V49 V159:V161" xr:uid="{15211EFD-2049-40DA-B54C-BAC6674745A7}">
+    <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="It should be in months" sqref="W97:W139 V2:V42 V47:V49 W159:W161" xr:uid="{15211EFD-2049-40DA-B54C-BAC6674745A7}">
       <formula1>1</formula1>
       <formula2>60</formula2>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="Kindly start will a capital letter for each country followed by small letters and separate with a comma if many countries are covered. " sqref="J97:J136 J25:J42 J47:J49 J138:J139 J2:J23" xr:uid="{720DDD97-1E13-49A5-A285-D20F37537F19}">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Hint" prompt="Kindly start will a capital letter for each country followed by small letters and separate with a comma if many countries are covered. " sqref="J97:J136 J25:J42 J47:J49 J138:J139 J2:J23 J159:J161" xr:uid="{720DDD97-1E13-49A5-A285-D20F37537F19}">
       <formula1>4</formula1>
       <formula2>250</formula2>
     </dataValidation>
-    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q47:Q49 Q97:Q139 Q2:Q42" xr:uid="{E595BC0B-8851-47EB-A6CF-9145865C838A}">
+    <dataValidation type="textLength" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q47:Q49 Q97:Q139 Q2:Q42 Q159:Q161" xr:uid="{E595BC0B-8851-47EB-A6CF-9145865C838A}">
       <formula1>3</formula1>
       <formula2>300</formula2>
     </dataValidation>
@@ -24709,7 +26123,7 @@
       <c r="A5" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="140" t="s">
+      <c r="B5" s="138" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="26" t="s">
@@ -24773,7 +26187,7 @@
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="140"/>
+      <c r="A10" s="138"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:E9" xr:uid="{B83AD578-DA28-4F78-8FD4-6B585E562D50}"/>
@@ -24783,17 +26197,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002408E3D2F54C53489D9AB6139CAEF0B9" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="492e2bda549b44b2f704032f7767c399">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d24e2f5-a44a-4509-8e3a-4f36d63f9f8f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="240da83a898570f75363da29bdb62103" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002408E3D2F54C53489D9AB6139CAEF0B9" ma:contentTypeVersion="3" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5b53137c13edb3a93c807c37fc810ee8">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9d24e2f5-a44a-4509-8e3a-4f36d63f9f8f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4989bacb2ae110786df28b14aa57fc34" ns2:_="">
     <xsd:import namespace="9d24e2f5-a44a-4509-8e3a-4f36d63f9f8f"/>
     <xsd:element name="properties">
       <xsd:complexType>
@@ -24929,6 +26334,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -24936,15 +26350,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83EAEF3C-2011-4D39-879E-EC8263732E2D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F46D618-D708-4DF1-99B7-BBB132EA2863}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{501692EB-DD9D-45CE-A8FF-2AFFA191EB74}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -24961,6 +26367,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{83EAEF3C-2011-4D39-879E-EC8263732E2D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5D7E94F3-90D7-4B0A-A68A-E7EE44295A2C}">
   <ds:schemaRefs>
